--- a/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/PseudoAnnotated/Pseudo_annotated.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/PseudoAnnotated/Pseudo_annotated.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AtsisiuntimasZiveDuomenu\PseudoAnnotated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06590343-B575-493C-BE1A-B8F31D6E4CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED57BDB-BBF8-4A36-89CC-A94574DE1B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2280" windowWidth="19200" windowHeight="7710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="240">
   <si>
     <t>filename</t>
   </si>
@@ -1163,10 +1163,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF55"/>
+  <dimension ref="A1:AE55"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.08984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="122.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1215,46 +1243,43 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="W1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>16</v>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="4"/>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4"/>
       <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>26</v>
       </c>
@@ -1339,7 +1364,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>34</v>
       </c>
@@ -1424,7 +1449,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>40</v>
       </c>
@@ -1506,7 +1531,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>45</v>
       </c>
@@ -1588,7 +1613,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>50</v>
       </c>
@@ -1670,7 +1695,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>55</v>
       </c>
@@ -1752,7 +1777,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>59</v>
       </c>
@@ -1832,7 +1857,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>62</v>
       </c>
@@ -1914,7 +1939,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>66</v>
       </c>
@@ -1996,7 +2021,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>70</v>
       </c>
@@ -2078,7 +2103,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>74</v>
       </c>
@@ -2160,7 +2185,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
@@ -2242,7 +2267,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>82</v>
       </c>
@@ -2322,7 +2347,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>85</v>
       </c>
@@ -2404,7 +2429,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>89</v>
       </c>

--- a/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/PseudoAnnotated/Pseudo_annotated.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/PseudoAnnotated/Pseudo_annotated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AtsisiuntimasZiveDuomenu\PseudoAnnotated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED57BDB-BBF8-4A36-89CC-A94574DE1B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4E7D6B-3C7B-4B33-98A0-EC1577CD3B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2280" windowWidth="19200" windowHeight="7710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="18600" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="244">
   <si>
     <t>filename</t>
   </si>
@@ -745,6 +745,18 @@
   </si>
   <si>
     <t>614dc6ff4bac1cd428017ed4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> out</t>
+  </si>
+  <si>
+    <t>rdr</t>
+  </si>
+  <si>
+    <t>noi</t>
+  </si>
+  <si>
+    <t>tp%</t>
   </si>
 </sst>
 </file>
@@ -770,7 +782,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -781,11 +793,6 @@
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E90FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -855,13 +862,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -870,19 +874,23 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1163,12 +1171,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE55"/>
+  <dimension ref="A1:AI55"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.36328125" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
@@ -1185,23 +1193,24 @@
     <col min="17" max="17" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.36328125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="25.36328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="122.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="10.453125" customWidth="1"/>
+    <col min="24" max="24" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="25" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="122.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1253,40 +1262,52 @@
         <v>19</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="AA1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B2">
         <v>575999</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D2">
@@ -1304,25 +1325,25 @@
       <c r="H2" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="5">
         <v>4850</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="5">
         <v>4849</v>
       </c>
-      <c r="K2" s="8">
-        <v>1</v>
-      </c>
-      <c r="L2" s="9">
+      <c r="K2" s="6">
+        <v>1</v>
+      </c>
+      <c r="L2" s="7">
         <v>0</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="6">
         <v>9</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="7">
         <v>0</v>
       </c>
       <c r="P2">
@@ -1334,44 +1355,56 @@
       <c r="R2">
         <v>0</v>
       </c>
-      <c r="S2" s="10">
-        <v>0</v>
-      </c>
-      <c r="T2" s="7">
-        <v>0</v>
-      </c>
-      <c r="U2" s="7">
-        <v>0</v>
-      </c>
-      <c r="V2" s="11">
-        <v>0</v>
-      </c>
-      <c r="W2" t="s">
+      <c r="S2" s="8">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5">
+        <v>0</v>
+      </c>
+      <c r="W2" s="8">
+        <v>0</v>
+      </c>
+      <c r="X2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="s">
         <v>30</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AB2" t="s">
         <v>31</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AC2" t="s">
         <v>32</v>
       </c>
-      <c r="Z2" s="4" t="s">
+      <c r="AD2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B3">
         <v>127999</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D3">
@@ -1389,25 +1422,25 @@
       <c r="H3" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="5">
         <v>797</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="5">
         <v>788</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="6">
         <v>5</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="7">
         <v>0</v>
       </c>
       <c r="M3">
         <v>4</v>
       </c>
-      <c r="N3" s="8">
+      <c r="N3" s="6">
         <v>7</v>
       </c>
-      <c r="O3" s="9">
+      <c r="O3" s="7">
         <v>0</v>
       </c>
       <c r="P3">
@@ -1419,44 +1452,56 @@
       <c r="R3">
         <v>8304</v>
       </c>
-      <c r="S3" s="10">
+      <c r="S3" s="8">
         <v>6.5</v>
       </c>
-      <c r="T3" s="7">
-        <v>0</v>
-      </c>
-      <c r="U3" s="7">
-        <v>0</v>
-      </c>
-      <c r="V3" s="11">
-        <v>0</v>
-      </c>
-      <c r="W3" t="s">
+      <c r="T3" s="5">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5">
+        <v>0</v>
+      </c>
+      <c r="W3" s="8">
+        <v>0</v>
+      </c>
+      <c r="X3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="s">
         <v>30</v>
       </c>
-      <c r="X3" t="s">
+      <c r="AB3" t="s">
         <v>37</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AC3" t="s">
         <v>38</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="AD3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AA3" s="4"/>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
         <v>40</v>
       </c>
       <c r="B4">
         <v>115199</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D4">
@@ -1471,25 +1516,25 @@
       <c r="H4" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="5">
         <v>763</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="5">
         <v>761</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="6">
         <v>2</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="7">
         <v>0</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
-      <c r="N4" s="8">
-        <v>0</v>
-      </c>
-      <c r="O4" s="9">
+      <c r="N4" s="6">
+        <v>0</v>
+      </c>
+      <c r="O4" s="7">
         <v>2</v>
       </c>
       <c r="P4">
@@ -1501,44 +1546,56 @@
       <c r="R4">
         <v>3762</v>
       </c>
-      <c r="S4" s="10">
+      <c r="S4" s="8">
         <v>3.3</v>
       </c>
-      <c r="T4" s="7">
-        <v>0</v>
-      </c>
-      <c r="U4" s="7">
-        <v>0</v>
-      </c>
-      <c r="V4" s="11">
-        <v>0</v>
-      </c>
-      <c r="W4" t="s">
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5">
+        <v>0</v>
+      </c>
+      <c r="W4" s="8">
+        <v>0</v>
+      </c>
+      <c r="X4" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="s">
         <v>30</v>
       </c>
-      <c r="X4" t="s">
+      <c r="AB4" t="s">
         <v>43</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="AC4" t="s">
         <v>38</v>
       </c>
-      <c r="Z4" s="13" t="s">
+      <c r="AD4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="3"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
         <v>45</v>
       </c>
       <c r="B5">
         <v>127999</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="14" t="s">
         <v>46</v>
       </c>
       <c r="D5">
@@ -1553,25 +1610,25 @@
       <c r="H5" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="5">
         <v>654</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="5">
         <v>651</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="6">
         <v>3</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="7">
         <v>0</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
-      <c r="N5" s="8">
-        <v>0</v>
-      </c>
-      <c r="O5" s="9">
+      <c r="N5" s="6">
+        <v>0</v>
+      </c>
+      <c r="O5" s="7">
         <v>0</v>
       </c>
       <c r="P5">
@@ -1583,44 +1640,56 @@
       <c r="R5">
         <v>0</v>
       </c>
-      <c r="S5" s="10">
-        <v>0</v>
-      </c>
-      <c r="T5" s="7">
-        <v>0</v>
-      </c>
-      <c r="U5" s="7">
-        <v>0</v>
-      </c>
-      <c r="V5" s="11">
-        <v>0</v>
-      </c>
-      <c r="W5" t="s">
+      <c r="S5" s="8">
+        <v>0</v>
+      </c>
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5">
+        <v>0</v>
+      </c>
+      <c r="W5" s="8">
+        <v>0</v>
+      </c>
+      <c r="X5" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="s">
         <v>30</v>
       </c>
-      <c r="X5" t="s">
+      <c r="AB5" t="s">
         <v>47</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="AC5" t="s">
         <v>48</v>
       </c>
-      <c r="Z5" s="4" t="s">
+      <c r="AD5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
-      <c r="AD5" s="4"/>
-      <c r="AE5" s="4"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="3"/>
+      <c r="AH5" s="3"/>
+      <c r="AI5" s="3"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>50</v>
       </c>
       <c r="B6">
         <v>127999</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D6">
@@ -1635,25 +1704,25 @@
       <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="5">
         <v>840</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="5">
         <v>817</v>
       </c>
-      <c r="K6" s="8">
-        <v>1</v>
-      </c>
-      <c r="L6" s="9">
+      <c r="K6" s="6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="7">
         <v>22</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
-      <c r="N6" s="8">
-        <v>0</v>
-      </c>
-      <c r="O6" s="9">
+      <c r="N6" s="6">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7">
         <v>9</v>
       </c>
       <c r="P6">
@@ -1665,44 +1734,56 @@
       <c r="R6">
         <v>0</v>
       </c>
-      <c r="S6" s="10">
-        <v>0</v>
-      </c>
-      <c r="T6" s="7">
-        <v>0</v>
-      </c>
-      <c r="U6" s="7">
-        <v>0</v>
-      </c>
-      <c r="V6" s="11">
-        <v>0</v>
-      </c>
-      <c r="W6" t="s">
+      <c r="S6" s="8">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5">
+        <v>0</v>
+      </c>
+      <c r="W6" s="8">
+        <v>0</v>
+      </c>
+      <c r="X6" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="s">
         <v>30</v>
       </c>
-      <c r="X6" t="s">
+      <c r="AB6" t="s">
         <v>52</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="AC6" t="s">
         <v>53</v>
       </c>
-      <c r="Z6" s="4" t="s">
+      <c r="AD6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="AA6" s="4"/>
-      <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
-      <c r="AD6" s="4"/>
-      <c r="AE6" s="4"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B7">
         <v>127999</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="14" t="s">
         <v>56</v>
       </c>
       <c r="D7">
@@ -1717,25 +1798,25 @@
       <c r="H7" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="5">
         <v>886</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="5">
         <v>876</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="6">
         <v>2</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="7">
         <v>8</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
-      <c r="N7" s="8">
-        <v>0</v>
-      </c>
-      <c r="O7" s="9">
+      <c r="N7" s="6">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7">
         <v>6</v>
       </c>
       <c r="P7">
@@ -1747,44 +1828,56 @@
       <c r="R7">
         <v>0</v>
       </c>
-      <c r="S7" s="10">
-        <v>0</v>
-      </c>
-      <c r="T7" s="7">
-        <v>0</v>
-      </c>
-      <c r="U7" s="7">
-        <v>0</v>
-      </c>
-      <c r="V7" s="11">
-        <v>0</v>
-      </c>
-      <c r="W7" t="s">
+      <c r="S7" s="8">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5">
+        <v>0</v>
+      </c>
+      <c r="W7" s="8">
+        <v>0</v>
+      </c>
+      <c r="X7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="s">
         <v>30</v>
       </c>
-      <c r="X7" t="s">
+      <c r="AB7" t="s">
         <v>57</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="AC7" t="s">
         <v>53</v>
       </c>
-      <c r="Z7" s="4" t="s">
+      <c r="AD7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="4"/>
-      <c r="AE7" s="4"/>
+      <c r="AE7" s="11"/>
+      <c r="AF7" s="11"/>
+      <c r="AG7" s="11"/>
+      <c r="AH7" s="3"/>
+      <c r="AI7" s="3"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>59</v>
       </c>
       <c r="B8">
         <v>127999</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="14" t="s">
         <v>60</v>
       </c>
       <c r="D8">
@@ -1799,25 +1892,25 @@
       <c r="H8" t="s">
         <v>29</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="5">
         <v>974</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="5">
         <v>967</v>
       </c>
-      <c r="K8" s="8">
-        <v>0</v>
-      </c>
-      <c r="L8" s="9">
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7">
         <v>7</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="6">
         <v>4</v>
       </c>
-      <c r="O8" s="9">
+      <c r="O8" s="7">
         <v>3</v>
       </c>
       <c r="P8">
@@ -1829,42 +1922,54 @@
       <c r="R8">
         <v>0</v>
       </c>
-      <c r="S8" s="10">
-        <v>0</v>
-      </c>
-      <c r="T8" s="7">
-        <v>0</v>
-      </c>
-      <c r="U8" s="7">
-        <v>0</v>
-      </c>
-      <c r="V8" s="11">
-        <v>0</v>
-      </c>
-      <c r="W8" t="s">
+      <c r="S8" s="8">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5">
+        <v>0</v>
+      </c>
+      <c r="W8" s="8">
+        <v>0</v>
+      </c>
+      <c r="X8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="s">
         <v>30</v>
       </c>
-      <c r="X8" t="s">
+      <c r="AB8" t="s">
         <v>61</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="AC8" t="s">
         <v>53</v>
       </c>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
-      <c r="AD8" s="4"/>
-      <c r="AE8" s="4"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3"/>
+      <c r="AI8" s="3"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
         <v>62</v>
       </c>
       <c r="B9">
         <v>127999</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="14" t="s">
         <v>63</v>
       </c>
       <c r="D9">
@@ -1879,25 +1984,25 @@
       <c r="H9" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="5">
         <v>835</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="5">
         <v>814</v>
       </c>
-      <c r="K9" s="8">
-        <v>0</v>
-      </c>
-      <c r="L9" s="9">
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7">
         <v>21</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
-      <c r="N9" s="8">
-        <v>1</v>
-      </c>
-      <c r="O9" s="9">
+      <c r="N9" s="6">
+        <v>1</v>
+      </c>
+      <c r="O9" s="7">
         <v>8</v>
       </c>
       <c r="P9">
@@ -1909,44 +2014,56 @@
       <c r="R9">
         <v>0</v>
       </c>
-      <c r="S9" s="10">
-        <v>0</v>
-      </c>
-      <c r="T9" s="7">
-        <v>0</v>
-      </c>
-      <c r="U9" s="7">
-        <v>0</v>
-      </c>
-      <c r="V9" s="11">
-        <v>0</v>
-      </c>
-      <c r="W9" t="s">
+      <c r="S9" s="8">
+        <v>0</v>
+      </c>
+      <c r="T9" s="5">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5">
+        <v>0</v>
+      </c>
+      <c r="W9" s="8">
+        <v>0</v>
+      </c>
+      <c r="X9" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="s">
         <v>30</v>
       </c>
-      <c r="X9" t="s">
+      <c r="AB9" t="s">
         <v>64</v>
       </c>
-      <c r="Y9" t="s">
+      <c r="AC9" t="s">
         <v>53</v>
       </c>
-      <c r="Z9" s="4" t="s">
+      <c r="AD9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA9" s="4"/>
-      <c r="AB9" s="4"/>
-      <c r="AC9" s="4"/>
-      <c r="AD9" s="4"/>
-      <c r="AE9" s="4"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3"/>
+      <c r="AH9" s="3"/>
+      <c r="AI9" s="3"/>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>66</v>
       </c>
       <c r="B10">
         <v>127999</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="14" t="s">
         <v>67</v>
       </c>
       <c r="D10">
@@ -1961,25 +2078,25 @@
       <c r="H10" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="5">
         <v>799</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="5">
         <v>796</v>
       </c>
-      <c r="K10" s="8">
-        <v>0</v>
-      </c>
-      <c r="L10" s="9">
+      <c r="K10" s="6">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
         <v>3</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="6">
         <v>2</v>
       </c>
-      <c r="O10" s="9">
+      <c r="O10" s="7">
         <v>2</v>
       </c>
       <c r="P10">
@@ -1991,44 +2108,56 @@
       <c r="R10">
         <v>1654</v>
       </c>
-      <c r="S10" s="10">
+      <c r="S10" s="8">
         <v>1.3</v>
       </c>
-      <c r="T10" s="7">
-        <v>0</v>
-      </c>
-      <c r="U10" s="7">
-        <v>0</v>
-      </c>
-      <c r="V10" s="11">
-        <v>0</v>
-      </c>
-      <c r="W10" t="s">
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5">
+        <v>0</v>
+      </c>
+      <c r="W10" s="8">
+        <v>0</v>
+      </c>
+      <c r="X10" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="s">
         <v>30</v>
       </c>
-      <c r="X10" t="s">
+      <c r="AB10" t="s">
         <v>68</v>
       </c>
-      <c r="Y10" t="s">
+      <c r="AC10" t="s">
         <v>53</v>
       </c>
-      <c r="Z10" s="4" t="s">
+      <c r="AD10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="AA10" s="4"/>
-      <c r="AB10" s="4"/>
-      <c r="AC10" s="4"/>
-      <c r="AD10" s="4"/>
-      <c r="AE10" s="4"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
+      <c r="AH10" s="3"/>
+      <c r="AI10" s="3"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B11">
         <v>127999</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="14" t="s">
         <v>71</v>
       </c>
       <c r="D11">
@@ -2043,25 +2172,25 @@
       <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="5">
         <v>738</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="5">
         <v>720</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="6">
         <v>4</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="7">
         <v>14</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
-      <c r="N11" s="8">
-        <v>0</v>
-      </c>
-      <c r="O11" s="9">
+      <c r="N11" s="6">
+        <v>0</v>
+      </c>
+      <c r="O11" s="7">
         <v>10</v>
       </c>
       <c r="P11">
@@ -2073,44 +2202,56 @@
       <c r="R11">
         <v>0</v>
       </c>
-      <c r="S11" s="10">
-        <v>0</v>
-      </c>
-      <c r="T11" s="7">
-        <v>0</v>
-      </c>
-      <c r="U11" s="7">
-        <v>0</v>
-      </c>
-      <c r="V11" s="11">
-        <v>0</v>
-      </c>
-      <c r="W11" t="s">
+      <c r="S11" s="8">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5">
+        <v>0</v>
+      </c>
+      <c r="W11" s="8">
+        <v>0</v>
+      </c>
+      <c r="X11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="s">
         <v>30</v>
       </c>
-      <c r="X11" t="s">
+      <c r="AB11" t="s">
         <v>72</v>
       </c>
-      <c r="Y11" t="s">
+      <c r="AC11" t="s">
         <v>53</v>
       </c>
-      <c r="Z11" s="4" t="s">
+      <c r="AD11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="AA11" s="4"/>
-      <c r="AB11" s="4"/>
-      <c r="AC11" s="4"/>
-      <c r="AD11" s="4"/>
-      <c r="AE11" s="4"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>74</v>
       </c>
       <c r="B12">
         <v>127999</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="14" t="s">
         <v>75</v>
       </c>
       <c r="D12">
@@ -2125,25 +2266,25 @@
       <c r="H12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="5">
         <v>821</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="5">
         <v>807</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="6">
         <v>2</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="7">
         <v>12</v>
       </c>
       <c r="M12">
         <v>0</v>
       </c>
-      <c r="N12" s="8">
-        <v>1</v>
-      </c>
-      <c r="O12" s="9">
+      <c r="N12" s="6">
+        <v>1</v>
+      </c>
+      <c r="O12" s="7">
         <v>5</v>
       </c>
       <c r="P12">
@@ -2155,44 +2296,56 @@
       <c r="R12">
         <v>0</v>
       </c>
-      <c r="S12" s="10">
-        <v>0</v>
-      </c>
-      <c r="T12" s="7">
-        <v>0</v>
-      </c>
-      <c r="U12" s="7">
-        <v>0</v>
-      </c>
-      <c r="V12" s="11">
-        <v>0</v>
-      </c>
-      <c r="W12" t="s">
+      <c r="S12" s="8">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5">
+        <v>0</v>
+      </c>
+      <c r="W12" s="8">
+        <v>0</v>
+      </c>
+      <c r="X12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="s">
         <v>30</v>
       </c>
-      <c r="X12" t="s">
+      <c r="AB12" t="s">
         <v>76</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="AC12" t="s">
         <v>53</v>
       </c>
-      <c r="Z12" s="4" t="s">
+      <c r="AD12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="AA12" s="4"/>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4"/>
-      <c r="AE12" s="4"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+      <c r="AH12" s="3"/>
+      <c r="AI12" s="3"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
         <v>78</v>
       </c>
       <c r="B13">
         <v>127999</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="14" t="s">
         <v>79</v>
       </c>
       <c r="D13">
@@ -2207,25 +2360,25 @@
       <c r="H13" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="5">
         <v>813</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="5">
         <v>799</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="6">
         <v>4</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="7">
         <v>10</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
-      <c r="N13" s="8">
-        <v>1</v>
-      </c>
-      <c r="O13" s="9">
+      <c r="N13" s="6">
+        <v>1</v>
+      </c>
+      <c r="O13" s="7">
         <v>9</v>
       </c>
       <c r="P13">
@@ -2237,44 +2390,56 @@
       <c r="R13">
         <v>0</v>
       </c>
-      <c r="S13" s="10">
-        <v>0</v>
-      </c>
-      <c r="T13" s="7">
-        <v>0</v>
-      </c>
-      <c r="U13" s="7">
-        <v>0</v>
-      </c>
-      <c r="V13" s="11">
-        <v>0</v>
-      </c>
-      <c r="W13" t="s">
+      <c r="S13" s="8">
+        <v>0</v>
+      </c>
+      <c r="T13" s="5">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5">
+        <v>0</v>
+      </c>
+      <c r="W13" s="8">
+        <v>0</v>
+      </c>
+      <c r="X13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="s">
         <v>30</v>
       </c>
-      <c r="X13" t="s">
+      <c r="AB13" t="s">
         <v>80</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="AC13" t="s">
         <v>53</v>
       </c>
-      <c r="Z13" s="4" t="s">
+      <c r="AD13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AA13" s="4"/>
-      <c r="AB13" s="4"/>
-      <c r="AC13" s="4"/>
-      <c r="AD13" s="4"/>
-      <c r="AE13" s="4"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="3"/>
+      <c r="AH13" s="3"/>
+      <c r="AI13" s="3"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B14">
         <v>127999</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="14" t="s">
         <v>83</v>
       </c>
       <c r="D14">
@@ -2289,25 +2454,25 @@
       <c r="H14" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="5">
         <v>756</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="5">
         <v>743</v>
       </c>
-      <c r="K14" s="8">
-        <v>1</v>
-      </c>
-      <c r="L14" s="9">
+      <c r="K14" s="6">
+        <v>1</v>
+      </c>
+      <c r="L14" s="7">
         <v>12</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
-      <c r="N14" s="8">
-        <v>1</v>
-      </c>
-      <c r="O14" s="9">
+      <c r="N14" s="6">
+        <v>1</v>
+      </c>
+      <c r="O14" s="7">
         <v>5</v>
       </c>
       <c r="P14">
@@ -2319,42 +2484,54 @@
       <c r="R14">
         <v>0</v>
       </c>
-      <c r="S14" s="10">
-        <v>0</v>
-      </c>
-      <c r="T14" s="7">
-        <v>0</v>
-      </c>
-      <c r="U14" s="7">
-        <v>0</v>
-      </c>
-      <c r="V14" s="11">
-        <v>0</v>
-      </c>
-      <c r="W14" t="s">
+      <c r="S14" s="8">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5">
+        <v>0</v>
+      </c>
+      <c r="W14" s="8">
+        <v>0</v>
+      </c>
+      <c r="X14" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="s">
         <v>30</v>
       </c>
-      <c r="X14" t="s">
+      <c r="AB14" t="s">
         <v>84</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="AC14" t="s">
         <v>53</v>
       </c>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
-      <c r="AB14" s="4"/>
-      <c r="AC14" s="4"/>
-      <c r="AD14" s="4"/>
-      <c r="AE14" s="4"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="3"/>
+      <c r="AH14" s="3"/>
+      <c r="AI14" s="3"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B15">
         <v>127999</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="14" t="s">
         <v>86</v>
       </c>
       <c r="D15">
@@ -2369,25 +2546,25 @@
       <c r="H15" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="5">
         <v>858</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="5">
         <v>848</v>
       </c>
-      <c r="K15" s="8">
-        <v>1</v>
-      </c>
-      <c r="L15" s="9">
+      <c r="K15" s="6">
+        <v>1</v>
+      </c>
+      <c r="L15" s="7">
         <v>9</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
-      <c r="N15" s="8">
-        <v>0</v>
-      </c>
-      <c r="O15" s="9">
+      <c r="N15" s="6">
+        <v>0</v>
+      </c>
+      <c r="O15" s="7">
         <v>4</v>
       </c>
       <c r="P15">
@@ -2399,44 +2576,56 @@
       <c r="R15">
         <v>0</v>
       </c>
-      <c r="S15" s="10">
-        <v>0</v>
-      </c>
-      <c r="T15" s="7">
-        <v>0</v>
-      </c>
-      <c r="U15" s="7">
-        <v>0</v>
-      </c>
-      <c r="V15" s="11">
-        <v>0</v>
-      </c>
-      <c r="W15" t="s">
+      <c r="S15" s="8">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5">
+        <v>0</v>
+      </c>
+      <c r="V15" s="5">
+        <v>0</v>
+      </c>
+      <c r="W15" s="8">
+        <v>0</v>
+      </c>
+      <c r="X15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="s">
         <v>30</v>
       </c>
-      <c r="X15" t="s">
+      <c r="AB15" t="s">
         <v>87</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="AC15" t="s">
         <v>53</v>
       </c>
-      <c r="Z15" s="4" t="s">
+      <c r="AD15" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="AA15" s="4"/>
-      <c r="AB15" s="4"/>
-      <c r="AC15" s="4"/>
-      <c r="AD15" s="4"/>
-      <c r="AE15" s="4"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="3"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
         <v>89</v>
       </c>
       <c r="B16">
         <v>127999</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="14" t="s">
         <v>90</v>
       </c>
       <c r="D16">
@@ -2451,25 +2640,25 @@
       <c r="H16" t="s">
         <v>29</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="5">
         <v>1037</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="5">
         <v>1019</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="6">
         <v>13</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="7">
         <v>0</v>
       </c>
       <c r="M16">
         <v>5</v>
       </c>
-      <c r="N16" s="8">
+      <c r="N16" s="6">
         <v>52</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="7">
         <v>7</v>
       </c>
       <c r="P16">
@@ -2481,44 +2670,56 @@
       <c r="R16">
         <v>5877</v>
       </c>
-      <c r="S16" s="10">
+      <c r="S16" s="8">
         <v>4.5999999999999996</v>
       </c>
-      <c r="T16" s="7">
-        <v>0</v>
-      </c>
-      <c r="U16" s="7">
-        <v>0</v>
-      </c>
-      <c r="V16" s="11">
-        <v>0</v>
-      </c>
-      <c r="W16" t="s">
+      <c r="T16" s="5">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5">
+        <v>0</v>
+      </c>
+      <c r="V16" s="5">
+        <v>0</v>
+      </c>
+      <c r="W16" s="8">
+        <v>0</v>
+      </c>
+      <c r="X16" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="s">
         <v>30</v>
       </c>
-      <c r="X16" t="s">
+      <c r="AB16" t="s">
         <v>91</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="AC16" t="s">
         <v>92</v>
       </c>
-      <c r="Z16" s="4" t="s">
+      <c r="AD16" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="AA16" s="4"/>
-      <c r="AB16" s="4"/>
-      <c r="AC16" s="4"/>
-      <c r="AD16" s="4"/>
-      <c r="AE16" s="4"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A17" s="12" t="s">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A17" s="10" t="s">
         <v>94</v>
       </c>
       <c r="B17">
         <v>127999</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="14" t="s">
         <v>95</v>
       </c>
       <c r="D17">
@@ -2533,25 +2734,25 @@
       <c r="H17" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="5">
         <v>929</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="5">
         <v>928</v>
       </c>
-      <c r="K17" s="8">
-        <v>1</v>
-      </c>
-      <c r="L17" s="9">
+      <c r="K17" s="6">
+        <v>1</v>
+      </c>
+      <c r="L17" s="7">
         <v>0</v>
       </c>
       <c r="M17">
         <v>0</v>
       </c>
-      <c r="N17" s="8">
+      <c r="N17" s="6">
         <v>6</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="7">
         <v>1</v>
       </c>
       <c r="P17">
@@ -2563,44 +2764,56 @@
       <c r="R17">
         <v>2578</v>
       </c>
-      <c r="S17" s="10">
+      <c r="S17" s="8">
         <v>2</v>
       </c>
-      <c r="T17" s="7">
-        <v>0</v>
-      </c>
-      <c r="U17" s="7">
-        <v>0</v>
-      </c>
-      <c r="V17" s="11">
-        <v>0</v>
-      </c>
-      <c r="W17" t="s">
+      <c r="T17" s="5">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5">
+        <v>0</v>
+      </c>
+      <c r="V17" s="5">
+        <v>0</v>
+      </c>
+      <c r="W17" s="8">
+        <v>0</v>
+      </c>
+      <c r="X17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="s">
         <v>30</v>
       </c>
-      <c r="X17" t="s">
+      <c r="AB17" t="s">
         <v>96</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="AC17" t="s">
         <v>92</v>
       </c>
-      <c r="Z17" s="4" t="s">
+      <c r="AD17" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AA17" s="4"/>
-      <c r="AB17" s="4"/>
-      <c r="AC17" s="4"/>
-      <c r="AD17" s="4"/>
-      <c r="AE17" s="4"/>
+      <c r="AE17" s="3"/>
+      <c r="AF17" s="3"/>
+      <c r="AG17" s="3"/>
+      <c r="AH17" s="3"/>
+      <c r="AI17" s="3"/>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A18" s="12" t="s">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
         <v>98</v>
       </c>
       <c r="B18">
         <v>127999</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="14" t="s">
         <v>99</v>
       </c>
       <c r="D18">
@@ -2615,25 +2828,25 @@
       <c r="H18" t="s">
         <v>29</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="5">
         <v>772</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J18" s="5">
         <v>767</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="6">
         <v>5</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="7">
         <v>0</v>
       </c>
       <c r="M18">
         <v>0</v>
       </c>
-      <c r="N18" s="8">
+      <c r="N18" s="6">
         <v>18</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="7">
         <v>1</v>
       </c>
       <c r="P18">
@@ -2645,44 +2858,56 @@
       <c r="R18">
         <v>46</v>
       </c>
-      <c r="S18" s="10">
-        <v>0</v>
-      </c>
-      <c r="T18" s="7">
-        <v>0</v>
-      </c>
-      <c r="U18" s="7">
-        <v>0</v>
-      </c>
-      <c r="V18" s="11">
-        <v>0</v>
-      </c>
-      <c r="W18" t="s">
+      <c r="S18" s="8">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5">
+        <v>0</v>
+      </c>
+      <c r="W18" s="8">
+        <v>0</v>
+      </c>
+      <c r="X18" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="s">
         <v>30</v>
       </c>
-      <c r="X18" t="s">
+      <c r="AB18" t="s">
         <v>100</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="AC18" t="s">
         <v>92</v>
       </c>
-      <c r="Z18" s="4" t="s">
+      <c r="AD18" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="AA18" s="4"/>
-      <c r="AB18" s="4"/>
-      <c r="AC18" s="4"/>
-      <c r="AD18" s="4"/>
-      <c r="AE18" s="4"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="3"/>
+      <c r="AH18" s="3"/>
+      <c r="AI18" s="3"/>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A19" s="12" t="s">
         <v>102</v>
       </c>
       <c r="B19">
         <v>127999</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="14" t="s">
         <v>103</v>
       </c>
       <c r="D19">
@@ -2700,25 +2925,25 @@
       <c r="H19" t="s">
         <v>42</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="5">
         <v>761</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="5">
         <v>756</v>
       </c>
-      <c r="K19" s="8">
-        <v>1</v>
-      </c>
-      <c r="L19" s="9">
+      <c r="K19" s="6">
+        <v>1</v>
+      </c>
+      <c r="L19" s="7">
         <v>4</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
-      <c r="N19" s="8">
-        <v>0</v>
-      </c>
-      <c r="O19" s="9">
+      <c r="N19" s="6">
+        <v>0</v>
+      </c>
+      <c r="O19" s="7">
         <v>3</v>
       </c>
       <c r="P19">
@@ -2730,44 +2955,56 @@
       <c r="R19">
         <v>1256</v>
       </c>
-      <c r="S19" s="10">
-        <v>1</v>
-      </c>
-      <c r="T19" s="7">
-        <v>0</v>
-      </c>
-      <c r="U19" s="7">
-        <v>0</v>
-      </c>
-      <c r="V19" s="11">
-        <v>0</v>
-      </c>
-      <c r="W19" t="s">
+      <c r="S19" s="8">
+        <v>1</v>
+      </c>
+      <c r="T19" s="5">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5">
+        <v>0</v>
+      </c>
+      <c r="W19" s="8">
+        <v>0</v>
+      </c>
+      <c r="X19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="s">
         <v>30</v>
       </c>
-      <c r="X19" t="s">
+      <c r="AB19" t="s">
         <v>105</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="AC19" t="s">
         <v>106</v>
       </c>
-      <c r="Z19" s="4" t="s">
+      <c r="AD19" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="AA19" s="4"/>
-      <c r="AB19" s="4"/>
-      <c r="AC19" s="4"/>
-      <c r="AD19" s="4"/>
-      <c r="AE19" s="4"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A20" s="14" t="s">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A20" s="12" t="s">
         <v>108</v>
       </c>
       <c r="B20">
         <v>127999</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="14" t="s">
         <v>109</v>
       </c>
       <c r="D20">
@@ -2785,25 +3022,25 @@
       <c r="H20" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="5">
         <v>646</v>
       </c>
-      <c r="J20" s="7">
+      <c r="J20" s="5">
         <v>644</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20" s="6">
         <v>2</v>
       </c>
-      <c r="L20" s="9">
+      <c r="L20" s="7">
         <v>0</v>
       </c>
       <c r="M20">
         <v>0</v>
       </c>
-      <c r="N20" s="8">
-        <v>1</v>
-      </c>
-      <c r="O20" s="9">
+      <c r="N20" s="6">
+        <v>1</v>
+      </c>
+      <c r="O20" s="7">
         <v>2</v>
       </c>
       <c r="P20">
@@ -2815,44 +3052,56 @@
       <c r="R20">
         <v>0</v>
       </c>
-      <c r="S20" s="10">
-        <v>0</v>
-      </c>
-      <c r="T20" s="7">
-        <v>0</v>
-      </c>
-      <c r="U20" s="7">
-        <v>0</v>
-      </c>
-      <c r="V20" s="11">
-        <v>0</v>
-      </c>
-      <c r="W20" t="s">
+      <c r="S20" s="8">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5">
+        <v>0</v>
+      </c>
+      <c r="W20" s="8">
+        <v>0</v>
+      </c>
+      <c r="X20" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="s">
         <v>30</v>
       </c>
-      <c r="X20" t="s">
+      <c r="AB20" t="s">
         <v>110</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="AC20" t="s">
         <v>106</v>
       </c>
-      <c r="Z20" s="4" t="s">
+      <c r="AD20" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="AA20" s="4"/>
-      <c r="AB20" s="4"/>
-      <c r="AC20" s="4"/>
-      <c r="AD20" s="4"/>
-      <c r="AE20" s="4"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="3"/>
+      <c r="AG20" s="3"/>
+      <c r="AH20" s="3"/>
+      <c r="AI20" s="3"/>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A21" s="14" t="s">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A21" s="12" t="s">
         <v>112</v>
       </c>
       <c r="B21">
         <v>127999</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="14" t="s">
         <v>113</v>
       </c>
       <c r="D21">
@@ -2870,25 +3119,25 @@
       <c r="H21" t="s">
         <v>42</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I21" s="5">
         <v>487</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J21" s="5">
         <v>485</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="6">
         <v>2</v>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="7">
         <v>0</v>
       </c>
       <c r="M21">
         <v>0</v>
       </c>
-      <c r="N21" s="8">
-        <v>0</v>
-      </c>
-      <c r="O21" s="9">
+      <c r="N21" s="6">
+        <v>0</v>
+      </c>
+      <c r="O21" s="7">
         <v>0</v>
       </c>
       <c r="P21">
@@ -2900,44 +3149,56 @@
       <c r="R21">
         <v>0</v>
       </c>
-      <c r="S21" s="10">
-        <v>0</v>
-      </c>
-      <c r="T21" s="7">
-        <v>0</v>
-      </c>
-      <c r="U21" s="7">
-        <v>0</v>
-      </c>
-      <c r="V21" s="11">
-        <v>0</v>
-      </c>
-      <c r="W21" t="s">
+      <c r="S21" s="8">
+        <v>0</v>
+      </c>
+      <c r="T21" s="5">
+        <v>0</v>
+      </c>
+      <c r="U21" s="5">
+        <v>0</v>
+      </c>
+      <c r="V21" s="5">
+        <v>0</v>
+      </c>
+      <c r="W21" s="8">
+        <v>0</v>
+      </c>
+      <c r="X21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="s">
         <v>30</v>
       </c>
-      <c r="X21" t="s">
+      <c r="AB21" t="s">
         <v>114</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="AC21" t="s">
         <v>106</v>
       </c>
-      <c r="Z21" s="4" t="s">
+      <c r="AD21" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="AA21" s="4"/>
-      <c r="AB21" s="4"/>
-      <c r="AC21" s="4"/>
-      <c r="AD21" s="4"/>
-      <c r="AE21" s="4"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3"/>
+      <c r="AH21" s="3"/>
+      <c r="AI21" s="3"/>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A22" s="12" t="s">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
         <v>116</v>
       </c>
       <c r="B22">
         <v>127999</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="14" t="s">
         <v>117</v>
       </c>
       <c r="D22">
@@ -2952,25 +3213,25 @@
       <c r="H22" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="5">
         <v>572</v>
       </c>
-      <c r="J22" s="7">
+      <c r="J22" s="5">
         <v>544</v>
       </c>
-      <c r="K22" s="8">
-        <v>0</v>
-      </c>
-      <c r="L22" s="9">
+      <c r="K22" s="6">
+        <v>0</v>
+      </c>
+      <c r="L22" s="7">
         <v>28</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
-      <c r="N22" s="8">
-        <v>0</v>
-      </c>
-      <c r="O22" s="9">
+      <c r="N22" s="6">
+        <v>0</v>
+      </c>
+      <c r="O22" s="7">
         <v>28</v>
       </c>
       <c r="P22">
@@ -2982,44 +3243,56 @@
       <c r="R22">
         <v>127</v>
       </c>
-      <c r="S22" s="10">
+      <c r="S22" s="8">
         <v>0.1</v>
       </c>
-      <c r="T22" s="7">
-        <v>0</v>
-      </c>
-      <c r="U22" s="7">
-        <v>0</v>
-      </c>
-      <c r="V22" s="11">
-        <v>0</v>
-      </c>
-      <c r="W22" t="s">
+      <c r="T22" s="5">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5">
+        <v>0</v>
+      </c>
+      <c r="V22" s="5">
+        <v>0</v>
+      </c>
+      <c r="W22" s="8">
+        <v>0</v>
+      </c>
+      <c r="X22" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="s">
         <v>30</v>
       </c>
-      <c r="X22" t="s">
+      <c r="AB22" t="s">
         <v>118</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="AC22" t="s">
         <v>119</v>
       </c>
-      <c r="Z22" s="4" t="s">
+      <c r="AD22" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AA22" s="4"/>
-      <c r="AB22" s="4"/>
-      <c r="AC22" s="4"/>
-      <c r="AD22" s="4"/>
-      <c r="AE22" s="4"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+      <c r="AH22" s="3"/>
+      <c r="AI22" s="3"/>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A23" s="12" t="s">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A23" s="10" t="s">
         <v>121</v>
       </c>
       <c r="B23">
         <v>127999</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="14" t="s">
         <v>122</v>
       </c>
       <c r="D23">
@@ -3034,25 +3307,25 @@
       <c r="H23" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I23" s="5">
         <v>652</v>
       </c>
-      <c r="J23" s="7">
+      <c r="J23" s="5">
         <v>624</v>
       </c>
-      <c r="K23" s="8">
-        <v>0</v>
-      </c>
-      <c r="L23" s="9">
+      <c r="K23" s="6">
+        <v>0</v>
+      </c>
+      <c r="L23" s="7">
         <v>28</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
-      <c r="N23" s="8">
-        <v>0</v>
-      </c>
-      <c r="O23" s="9">
+      <c r="N23" s="6">
+        <v>0</v>
+      </c>
+      <c r="O23" s="7">
         <v>20</v>
       </c>
       <c r="P23">
@@ -3064,44 +3337,56 @@
       <c r="R23">
         <v>121</v>
       </c>
-      <c r="S23" s="10">
+      <c r="S23" s="8">
         <v>0.1</v>
       </c>
-      <c r="T23" s="7">
-        <v>0</v>
-      </c>
-      <c r="U23" s="7">
-        <v>0</v>
-      </c>
-      <c r="V23" s="11">
-        <v>0</v>
-      </c>
-      <c r="W23" t="s">
+      <c r="T23" s="5">
+        <v>0</v>
+      </c>
+      <c r="U23" s="5">
+        <v>0</v>
+      </c>
+      <c r="V23" s="5">
+        <v>0</v>
+      </c>
+      <c r="W23" s="8">
+        <v>0</v>
+      </c>
+      <c r="X23" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="s">
         <v>30</v>
       </c>
-      <c r="X23" t="s">
+      <c r="AB23" t="s">
         <v>123</v>
       </c>
-      <c r="Y23" t="s">
+      <c r="AC23" t="s">
         <v>119</v>
       </c>
-      <c r="Z23" s="4" t="s">
+      <c r="AD23" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AA23" s="4"/>
-      <c r="AB23" s="4"/>
-      <c r="AC23" s="4"/>
-      <c r="AD23" s="4"/>
-      <c r="AE23" s="4"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3"/>
+      <c r="AH23" s="3"/>
+      <c r="AI23" s="3"/>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A24" s="12" t="s">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A24" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B24">
         <v>127999</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="14" t="s">
         <v>125</v>
       </c>
       <c r="D24">
@@ -3116,25 +3401,25 @@
       <c r="H24" t="s">
         <v>29</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I24" s="5">
         <v>584</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J24" s="5">
         <v>562</v>
       </c>
-      <c r="K24" s="8">
-        <v>0</v>
-      </c>
-      <c r="L24" s="9">
+      <c r="K24" s="6">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7">
         <v>22</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
-      <c r="N24" s="8">
-        <v>0</v>
-      </c>
-      <c r="O24" s="9">
+      <c r="N24" s="6">
+        <v>0</v>
+      </c>
+      <c r="O24" s="7">
         <v>22</v>
       </c>
       <c r="P24">
@@ -3146,44 +3431,56 @@
       <c r="R24">
         <v>0</v>
       </c>
-      <c r="S24" s="10">
-        <v>0</v>
-      </c>
-      <c r="T24" s="7">
-        <v>0</v>
-      </c>
-      <c r="U24" s="7">
-        <v>0</v>
-      </c>
-      <c r="V24" s="11">
-        <v>0</v>
-      </c>
-      <c r="W24" t="s">
+      <c r="S24" s="8">
+        <v>0</v>
+      </c>
+      <c r="T24" s="5">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5">
+        <v>0</v>
+      </c>
+      <c r="V24" s="5">
+        <v>0</v>
+      </c>
+      <c r="W24" s="8">
+        <v>0</v>
+      </c>
+      <c r="X24" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="s">
         <v>30</v>
       </c>
-      <c r="X24" t="s">
+      <c r="AB24" t="s">
         <v>126</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="AC24" t="s">
         <v>119</v>
       </c>
-      <c r="Z24" s="4" t="s">
+      <c r="AD24" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="AA24" s="4"/>
-      <c r="AB24" s="4"/>
-      <c r="AC24" s="4"/>
-      <c r="AD24" s="4"/>
-      <c r="AE24" s="4"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
+      <c r="AH24" s="3"/>
+      <c r="AI24" s="3"/>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A25" s="12" t="s">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A25" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B25">
         <v>127999</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="14" t="s">
         <v>129</v>
       </c>
       <c r="D25">
@@ -3198,25 +3495,25 @@
       <c r="H25" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="7">
+      <c r="I25" s="5">
         <v>645</v>
       </c>
-      <c r="J25" s="7">
+      <c r="J25" s="5">
         <v>628</v>
       </c>
-      <c r="K25" s="8">
-        <v>0</v>
-      </c>
-      <c r="L25" s="9">
+      <c r="K25" s="6">
+        <v>0</v>
+      </c>
+      <c r="L25" s="7">
         <v>17</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
-      <c r="N25" s="8">
-        <v>1</v>
-      </c>
-      <c r="O25" s="9">
+      <c r="N25" s="6">
+        <v>1</v>
+      </c>
+      <c r="O25" s="7">
         <v>17</v>
       </c>
       <c r="P25">
@@ -3228,44 +3525,56 @@
       <c r="R25">
         <v>1285</v>
       </c>
-      <c r="S25" s="10">
-        <v>1</v>
-      </c>
-      <c r="T25" s="7">
-        <v>0</v>
-      </c>
-      <c r="U25" s="7">
-        <v>0</v>
-      </c>
-      <c r="V25" s="11">
-        <v>0</v>
-      </c>
-      <c r="W25" t="s">
+      <c r="S25" s="8">
+        <v>1</v>
+      </c>
+      <c r="T25" s="5">
+        <v>0</v>
+      </c>
+      <c r="U25" s="5">
+        <v>0</v>
+      </c>
+      <c r="V25" s="5">
+        <v>0</v>
+      </c>
+      <c r="W25" s="8">
+        <v>0</v>
+      </c>
+      <c r="X25" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="s">
         <v>30</v>
       </c>
-      <c r="X25" t="s">
+      <c r="AB25" t="s">
         <v>130</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="AC25" t="s">
         <v>119</v>
       </c>
-      <c r="Z25" s="4" t="s">
+      <c r="AD25" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AA25" s="4"/>
-      <c r="AB25" s="4"/>
-      <c r="AC25" s="4"/>
-      <c r="AD25" s="4"/>
-      <c r="AE25" s="4"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="3"/>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A26" s="12" t="s">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
         <v>132</v>
       </c>
       <c r="B26">
         <v>127999</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="14" t="s">
         <v>133</v>
       </c>
       <c r="D26">
@@ -3280,25 +3589,25 @@
       <c r="H26" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I26" s="5">
         <v>690</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J26" s="5">
         <v>675</v>
       </c>
-      <c r="K26" s="8">
-        <v>0</v>
-      </c>
-      <c r="L26" s="9">
+      <c r="K26" s="6">
+        <v>0</v>
+      </c>
+      <c r="L26" s="7">
         <v>15</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
-      <c r="N26" s="8">
-        <v>0</v>
-      </c>
-      <c r="O26" s="9">
+      <c r="N26" s="6">
+        <v>0</v>
+      </c>
+      <c r="O26" s="7">
         <v>15</v>
       </c>
       <c r="P26">
@@ -3310,44 +3619,56 @@
       <c r="R26">
         <v>14</v>
       </c>
-      <c r="S26" s="10">
-        <v>0</v>
-      </c>
-      <c r="T26" s="7">
-        <v>0</v>
-      </c>
-      <c r="U26" s="7">
-        <v>0</v>
-      </c>
-      <c r="V26" s="11">
-        <v>0</v>
-      </c>
-      <c r="W26" t="s">
+      <c r="S26" s="8">
+        <v>0</v>
+      </c>
+      <c r="T26" s="5">
+        <v>0</v>
+      </c>
+      <c r="U26" s="5">
+        <v>0</v>
+      </c>
+      <c r="V26" s="5">
+        <v>0</v>
+      </c>
+      <c r="W26" s="8">
+        <v>0</v>
+      </c>
+      <c r="X26" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="s">
         <v>30</v>
       </c>
-      <c r="X26" t="s">
+      <c r="AB26" t="s">
         <v>134</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="AC26" t="s">
         <v>119</v>
       </c>
-      <c r="Z26" s="4" t="s">
+      <c r="AD26" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AA26" s="4"/>
-      <c r="AB26" s="4"/>
-      <c r="AC26" s="4"/>
-      <c r="AD26" s="4"/>
-      <c r="AE26" s="4"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="3"/>
+      <c r="AG26" s="3"/>
+      <c r="AH26" s="3"/>
+      <c r="AI26" s="3"/>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A27" s="12" t="s">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A27" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B27">
         <v>127999</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="14" t="s">
         <v>137</v>
       </c>
       <c r="D27">
@@ -3362,25 +3683,25 @@
       <c r="H27" t="s">
         <v>29</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I27" s="5">
         <v>638</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J27" s="5">
         <v>626</v>
       </c>
-      <c r="K27" s="8">
-        <v>0</v>
-      </c>
-      <c r="L27" s="9">
+      <c r="K27" s="6">
+        <v>0</v>
+      </c>
+      <c r="L27" s="7">
         <v>12</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
-      <c r="N27" s="8">
-        <v>0</v>
-      </c>
-      <c r="O27" s="9">
+      <c r="N27" s="6">
+        <v>0</v>
+      </c>
+      <c r="O27" s="7">
         <v>12</v>
       </c>
       <c r="P27">
@@ -3392,44 +3713,56 @@
       <c r="R27">
         <v>0</v>
       </c>
-      <c r="S27" s="10">
-        <v>0</v>
-      </c>
-      <c r="T27" s="7">
-        <v>0</v>
-      </c>
-      <c r="U27" s="7">
-        <v>0</v>
-      </c>
-      <c r="V27" s="11">
-        <v>0</v>
-      </c>
-      <c r="W27" t="s">
+      <c r="S27" s="8">
+        <v>0</v>
+      </c>
+      <c r="T27" s="5">
+        <v>0</v>
+      </c>
+      <c r="U27" s="5">
+        <v>0</v>
+      </c>
+      <c r="V27" s="5">
+        <v>0</v>
+      </c>
+      <c r="W27" s="8">
+        <v>0</v>
+      </c>
+      <c r="X27" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="s">
         <v>30</v>
       </c>
-      <c r="X27" t="s">
+      <c r="AB27" t="s">
         <v>138</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="AC27" t="s">
         <v>119</v>
       </c>
-      <c r="Z27" s="4" t="s">
+      <c r="AD27" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AA27" s="4"/>
-      <c r="AB27" s="4"/>
-      <c r="AC27" s="4"/>
-      <c r="AD27" s="4"/>
-      <c r="AE27" s="4"/>
+      <c r="AE27" s="3"/>
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="3"/>
+      <c r="AH27" s="3"/>
+      <c r="AI27" s="3"/>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A28" s="12" t="s">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A28" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B28">
         <v>127999</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D28">
@@ -3444,25 +3777,25 @@
       <c r="H28" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="7">
+      <c r="I28" s="5">
         <v>639</v>
       </c>
-      <c r="J28" s="7">
+      <c r="J28" s="5">
         <v>627</v>
       </c>
-      <c r="K28" s="8">
-        <v>0</v>
-      </c>
-      <c r="L28" s="9">
+      <c r="K28" s="6">
+        <v>0</v>
+      </c>
+      <c r="L28" s="7">
         <v>12</v>
       </c>
       <c r="M28">
         <v>0</v>
       </c>
-      <c r="N28" s="8">
-        <v>0</v>
-      </c>
-      <c r="O28" s="9">
+      <c r="N28" s="6">
+        <v>0</v>
+      </c>
+      <c r="O28" s="7">
         <v>13</v>
       </c>
       <c r="P28">
@@ -3474,44 +3807,56 @@
       <c r="R28">
         <v>44</v>
       </c>
-      <c r="S28" s="10">
-        <v>0</v>
-      </c>
-      <c r="T28" s="7">
-        <v>0</v>
-      </c>
-      <c r="U28" s="7">
-        <v>0</v>
-      </c>
-      <c r="V28" s="11">
-        <v>0</v>
-      </c>
-      <c r="W28" t="s">
+      <c r="S28" s="8">
+        <v>0</v>
+      </c>
+      <c r="T28" s="5">
+        <v>0</v>
+      </c>
+      <c r="U28" s="5">
+        <v>0</v>
+      </c>
+      <c r="V28" s="5">
+        <v>0</v>
+      </c>
+      <c r="W28" s="8">
+        <v>0</v>
+      </c>
+      <c r="X28" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="s">
         <v>30</v>
       </c>
-      <c r="X28" t="s">
+      <c r="AB28" t="s">
         <v>141</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="AC28" t="s">
         <v>119</v>
       </c>
-      <c r="Z28" s="4" t="s">
+      <c r="AD28" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="AA28" s="4"/>
-      <c r="AB28" s="4"/>
-      <c r="AC28" s="4"/>
-      <c r="AD28" s="4"/>
-      <c r="AE28" s="4"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="3"/>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3"/>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A29" s="12" t="s">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
         <v>143</v>
       </c>
       <c r="B29">
         <v>127999</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="14" t="s">
         <v>144</v>
       </c>
       <c r="D29">
@@ -3526,25 +3871,25 @@
       <c r="H29" t="s">
         <v>29</v>
       </c>
-      <c r="I29" s="7">
+      <c r="I29" s="5">
         <v>555</v>
       </c>
-      <c r="J29" s="7">
+      <c r="J29" s="5">
         <v>545</v>
       </c>
-      <c r="K29" s="8">
-        <v>0</v>
-      </c>
-      <c r="L29" s="9">
+      <c r="K29" s="6">
+        <v>0</v>
+      </c>
+      <c r="L29" s="7">
         <v>10</v>
       </c>
       <c r="M29">
         <v>0</v>
       </c>
-      <c r="N29" s="8">
-        <v>0</v>
-      </c>
-      <c r="O29" s="9">
+      <c r="N29" s="6">
+        <v>0</v>
+      </c>
+      <c r="O29" s="7">
         <v>12</v>
       </c>
       <c r="P29">
@@ -3556,44 +3901,56 @@
       <c r="R29">
         <v>299</v>
       </c>
-      <c r="S29" s="10">
+      <c r="S29" s="8">
         <v>0.2</v>
       </c>
-      <c r="T29" s="7">
-        <v>0</v>
-      </c>
-      <c r="U29" s="7">
-        <v>0</v>
-      </c>
-      <c r="V29" s="11">
-        <v>0</v>
-      </c>
-      <c r="W29" t="s">
+      <c r="T29" s="5">
+        <v>0</v>
+      </c>
+      <c r="U29" s="5">
+        <v>0</v>
+      </c>
+      <c r="V29" s="5">
+        <v>0</v>
+      </c>
+      <c r="W29" s="8">
+        <v>0</v>
+      </c>
+      <c r="X29" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="s">
         <v>30</v>
       </c>
-      <c r="X29" t="s">
+      <c r="AB29" t="s">
         <v>145</v>
       </c>
-      <c r="Y29" t="s">
+      <c r="AC29" t="s">
         <v>119</v>
       </c>
-      <c r="Z29" s="4" t="s">
+      <c r="AD29" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AA29" s="4"/>
-      <c r="AB29" s="4"/>
-      <c r="AC29" s="4"/>
-      <c r="AD29" s="4"/>
-      <c r="AE29" s="4"/>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="3"/>
+      <c r="AH29" s="3"/>
+      <c r="AI29" s="3"/>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A30" s="12" t="s">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A30" s="10" t="s">
         <v>146</v>
       </c>
       <c r="B30">
         <v>127999</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="14" t="s">
         <v>147</v>
       </c>
       <c r="D30">
@@ -3608,25 +3965,25 @@
       <c r="H30" t="s">
         <v>29</v>
       </c>
-      <c r="I30" s="7">
+      <c r="I30" s="5">
         <v>712</v>
       </c>
-      <c r="J30" s="7">
+      <c r="J30" s="5">
         <v>707</v>
       </c>
-      <c r="K30" s="8">
-        <v>0</v>
-      </c>
-      <c r="L30" s="9">
+      <c r="K30" s="6">
+        <v>0</v>
+      </c>
+      <c r="L30" s="7">
         <v>5</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
-      <c r="N30" s="8">
+      <c r="N30" s="6">
         <v>2</v>
       </c>
-      <c r="O30" s="9">
+      <c r="O30" s="7">
         <v>5</v>
       </c>
       <c r="P30">
@@ -3638,44 +3995,56 @@
       <c r="R30">
         <v>2109</v>
       </c>
-      <c r="S30" s="10">
+      <c r="S30" s="8">
         <v>1.6</v>
       </c>
-      <c r="T30" s="7">
-        <v>0</v>
-      </c>
-      <c r="U30" s="7">
-        <v>0</v>
-      </c>
-      <c r="V30" s="11">
-        <v>0</v>
-      </c>
-      <c r="W30" t="s">
+      <c r="T30" s="5">
+        <v>0</v>
+      </c>
+      <c r="U30" s="5">
+        <v>0</v>
+      </c>
+      <c r="V30" s="5">
+        <v>0</v>
+      </c>
+      <c r="W30" s="8">
+        <v>0</v>
+      </c>
+      <c r="X30" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="s">
         <v>30</v>
       </c>
-      <c r="X30" t="s">
+      <c r="AB30" t="s">
         <v>148</v>
       </c>
-      <c r="Y30" t="s">
+      <c r="AC30" t="s">
         <v>119</v>
       </c>
-      <c r="Z30" s="4" t="s">
+      <c r="AD30" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="AA30" s="4"/>
-      <c r="AB30" s="4"/>
-      <c r="AC30" s="4"/>
-      <c r="AD30" s="4"/>
-      <c r="AE30" s="4"/>
+      <c r="AE30" s="3"/>
+      <c r="AF30" s="3"/>
+      <c r="AG30" s="3"/>
+      <c r="AH30" s="3"/>
+      <c r="AI30" s="3"/>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A31" s="12" t="s">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
         <v>150</v>
       </c>
       <c r="B31">
         <v>127999</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="14" t="s">
         <v>151</v>
       </c>
       <c r="D31">
@@ -3690,25 +4059,25 @@
       <c r="H31" t="s">
         <v>29</v>
       </c>
-      <c r="I31" s="7">
+      <c r="I31" s="5">
         <v>712</v>
       </c>
-      <c r="J31" s="7">
+      <c r="J31" s="5">
         <v>707</v>
       </c>
-      <c r="K31" s="8">
-        <v>0</v>
-      </c>
-      <c r="L31" s="9">
+      <c r="K31" s="6">
+        <v>0</v>
+      </c>
+      <c r="L31" s="7">
         <v>5</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
-      <c r="N31" s="8">
-        <v>0</v>
-      </c>
-      <c r="O31" s="9">
+      <c r="N31" s="6">
+        <v>0</v>
+      </c>
+      <c r="O31" s="7">
         <v>2</v>
       </c>
       <c r="P31">
@@ -3720,44 +4089,56 @@
       <c r="R31">
         <v>240</v>
       </c>
-      <c r="S31" s="10">
+      <c r="S31" s="8">
         <v>0.2</v>
       </c>
-      <c r="T31" s="7">
-        <v>0</v>
-      </c>
-      <c r="U31" s="7">
-        <v>0</v>
-      </c>
-      <c r="V31" s="11">
-        <v>0</v>
-      </c>
-      <c r="W31" t="s">
+      <c r="T31" s="5">
+        <v>0</v>
+      </c>
+      <c r="U31" s="5">
+        <v>0</v>
+      </c>
+      <c r="V31" s="5">
+        <v>0</v>
+      </c>
+      <c r="W31" s="8">
+        <v>0</v>
+      </c>
+      <c r="X31" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="s">
         <v>30</v>
       </c>
-      <c r="X31" t="s">
+      <c r="AB31" t="s">
         <v>152</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="AC31" t="s">
         <v>119</v>
       </c>
-      <c r="Z31" s="4" t="s">
+      <c r="AD31" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AA31" s="4"/>
-      <c r="AB31" s="4"/>
-      <c r="AC31" s="4"/>
-      <c r="AD31" s="4"/>
-      <c r="AE31" s="4"/>
+      <c r="AE31" s="3"/>
+      <c r="AF31" s="3"/>
+      <c r="AG31" s="3"/>
+      <c r="AH31" s="3"/>
+      <c r="AI31" s="3"/>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A32" s="12" t="s">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A32" s="10" t="s">
         <v>153</v>
       </c>
       <c r="B32">
         <v>127999</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="14" t="s">
         <v>154</v>
       </c>
       <c r="D32">
@@ -3772,25 +4153,25 @@
       <c r="H32" t="s">
         <v>29</v>
       </c>
-      <c r="I32" s="7">
+      <c r="I32" s="5">
         <v>721</v>
       </c>
-      <c r="J32" s="7">
+      <c r="J32" s="5">
         <v>717</v>
       </c>
-      <c r="K32" s="8">
-        <v>0</v>
-      </c>
-      <c r="L32" s="9">
+      <c r="K32" s="6">
+        <v>0</v>
+      </c>
+      <c r="L32" s="7">
         <v>4</v>
       </c>
       <c r="M32">
         <v>0</v>
       </c>
-      <c r="N32" s="8">
-        <v>0</v>
-      </c>
-      <c r="O32" s="9">
+      <c r="N32" s="6">
+        <v>0</v>
+      </c>
+      <c r="O32" s="7">
         <v>5</v>
       </c>
       <c r="P32">
@@ -3802,44 +4183,56 @@
       <c r="R32">
         <v>121</v>
       </c>
-      <c r="S32" s="10">
+      <c r="S32" s="8">
         <v>0.1</v>
       </c>
-      <c r="T32" s="7">
-        <v>0</v>
-      </c>
-      <c r="U32" s="7">
-        <v>0</v>
-      </c>
-      <c r="V32" s="11">
-        <v>0</v>
-      </c>
-      <c r="W32" t="s">
+      <c r="T32" s="5">
+        <v>0</v>
+      </c>
+      <c r="U32" s="5">
+        <v>0</v>
+      </c>
+      <c r="V32" s="5">
+        <v>0</v>
+      </c>
+      <c r="W32" s="8">
+        <v>0</v>
+      </c>
+      <c r="X32" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="s">
         <v>30</v>
       </c>
-      <c r="X32" t="s">
+      <c r="AB32" t="s">
         <v>155</v>
       </c>
-      <c r="Y32" t="s">
+      <c r="AC32" t="s">
         <v>119</v>
       </c>
-      <c r="Z32" s="4" t="s">
+      <c r="AD32" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AA32" s="4"/>
-      <c r="AB32" s="4"/>
-      <c r="AC32" s="4"/>
-      <c r="AD32" s="4"/>
-      <c r="AE32" s="4"/>
+      <c r="AE32" s="3"/>
+      <c r="AF32" s="3"/>
+      <c r="AG32" s="3"/>
+      <c r="AH32" s="3"/>
+      <c r="AI32" s="3"/>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A33" s="12" t="s">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A33" s="10" t="s">
         <v>156</v>
       </c>
       <c r="B33">
         <v>127999</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="14" t="s">
         <v>157</v>
       </c>
       <c r="D33">
@@ -3854,25 +4247,25 @@
       <c r="H33" t="s">
         <v>29</v>
       </c>
-      <c r="I33" s="7">
+      <c r="I33" s="5">
         <v>737</v>
       </c>
-      <c r="J33" s="7">
+      <c r="J33" s="5">
         <v>734</v>
       </c>
-      <c r="K33" s="8">
-        <v>0</v>
-      </c>
-      <c r="L33" s="9">
+      <c r="K33" s="6">
+        <v>0</v>
+      </c>
+      <c r="L33" s="7">
         <v>3</v>
       </c>
       <c r="M33">
         <v>0</v>
       </c>
-      <c r="N33" s="8">
-        <v>1</v>
-      </c>
-      <c r="O33" s="9">
+      <c r="N33" s="6">
+        <v>1</v>
+      </c>
+      <c r="O33" s="7">
         <v>3</v>
       </c>
       <c r="P33">
@@ -3884,44 +4277,56 @@
       <c r="R33">
         <v>0</v>
       </c>
-      <c r="S33" s="10">
-        <v>0</v>
-      </c>
-      <c r="T33" s="7">
-        <v>0</v>
-      </c>
-      <c r="U33" s="7">
-        <v>0</v>
-      </c>
-      <c r="V33" s="11">
-        <v>0</v>
-      </c>
-      <c r="W33" t="s">
+      <c r="S33" s="8">
+        <v>0</v>
+      </c>
+      <c r="T33" s="5">
+        <v>0</v>
+      </c>
+      <c r="U33" s="5">
+        <v>0</v>
+      </c>
+      <c r="V33" s="5">
+        <v>0</v>
+      </c>
+      <c r="W33" s="8">
+        <v>0</v>
+      </c>
+      <c r="X33" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="s">
         <v>30</v>
       </c>
-      <c r="X33" t="s">
+      <c r="AB33" t="s">
         <v>158</v>
       </c>
-      <c r="Y33" t="s">
+      <c r="AC33" t="s">
         <v>119</v>
       </c>
-      <c r="Z33" s="4" t="s">
+      <c r="AD33" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="AA33" s="4"/>
-      <c r="AB33" s="4"/>
-      <c r="AC33" s="4"/>
-      <c r="AD33" s="4"/>
-      <c r="AE33" s="4"/>
+      <c r="AE33" s="3"/>
+      <c r="AF33" s="3"/>
+      <c r="AG33" s="3"/>
+      <c r="AH33" s="3"/>
+      <c r="AI33" s="3"/>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A34" s="12" t="s">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A34" s="10" t="s">
         <v>160</v>
       </c>
       <c r="B34">
         <v>127999</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="14" t="s">
         <v>161</v>
       </c>
       <c r="D34">
@@ -3936,25 +4341,25 @@
       <c r="H34" t="s">
         <v>29</v>
       </c>
-      <c r="I34" s="7">
+      <c r="I34" s="5">
         <v>574</v>
       </c>
-      <c r="J34" s="7">
+      <c r="J34" s="5">
         <v>573</v>
       </c>
-      <c r="K34" s="8">
-        <v>0</v>
-      </c>
-      <c r="L34" s="9">
+      <c r="K34" s="6">
+        <v>0</v>
+      </c>
+      <c r="L34" s="7">
         <v>1</v>
       </c>
       <c r="M34">
         <v>0</v>
       </c>
-      <c r="N34" s="8">
+      <c r="N34" s="6">
         <v>2</v>
       </c>
-      <c r="O34" s="9">
+      <c r="O34" s="7">
         <v>1</v>
       </c>
       <c r="P34">
@@ -3966,44 +4371,56 @@
       <c r="R34">
         <v>95</v>
       </c>
-      <c r="S34" s="10">
+      <c r="S34" s="8">
         <v>0.1</v>
       </c>
-      <c r="T34" s="7">
-        <v>0</v>
-      </c>
-      <c r="U34" s="7">
-        <v>0</v>
-      </c>
-      <c r="V34" s="11">
-        <v>0</v>
-      </c>
-      <c r="W34" t="s">
+      <c r="T34" s="5">
+        <v>0</v>
+      </c>
+      <c r="U34" s="5">
+        <v>0</v>
+      </c>
+      <c r="V34" s="5">
+        <v>0</v>
+      </c>
+      <c r="W34" s="8">
+        <v>0</v>
+      </c>
+      <c r="X34" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="s">
         <v>30</v>
       </c>
-      <c r="X34" t="s">
+      <c r="AB34" t="s">
         <v>162</v>
       </c>
-      <c r="Y34" t="s">
+      <c r="AC34" t="s">
         <v>119</v>
       </c>
-      <c r="Z34" s="4" t="s">
+      <c r="AD34" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="AA34" s="4"/>
-      <c r="AB34" s="4"/>
-      <c r="AC34" s="4"/>
-      <c r="AD34" s="4"/>
-      <c r="AE34" s="4"/>
+      <c r="AE34" s="3"/>
+      <c r="AF34" s="3"/>
+      <c r="AG34" s="3"/>
+      <c r="AH34" s="3"/>
+      <c r="AI34" s="3"/>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A35" s="14" t="s">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A35" s="12" t="s">
         <v>164</v>
       </c>
       <c r="B35">
         <v>127999</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="14" t="s">
         <v>165</v>
       </c>
       <c r="D35">
@@ -4021,25 +4438,25 @@
       <c r="H35" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="7">
+      <c r="I35" s="5">
         <v>903</v>
       </c>
-      <c r="J35" s="7">
+      <c r="J35" s="5">
         <v>903</v>
       </c>
-      <c r="K35" s="8">
-        <v>0</v>
-      </c>
-      <c r="L35" s="9">
+      <c r="K35" s="6">
+        <v>0</v>
+      </c>
+      <c r="L35" s="7">
         <v>0</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
-      <c r="N35" s="8">
+      <c r="N35" s="6">
         <v>2</v>
       </c>
-      <c r="O35" s="9">
+      <c r="O35" s="7">
         <v>0</v>
       </c>
       <c r="P35">
@@ -4051,42 +4468,54 @@
       <c r="R35">
         <v>0</v>
       </c>
-      <c r="S35" s="10">
-        <v>0</v>
-      </c>
-      <c r="T35" s="7">
-        <v>0</v>
-      </c>
-      <c r="U35" s="7">
-        <v>0</v>
-      </c>
-      <c r="V35" s="11">
-        <v>0</v>
-      </c>
-      <c r="W35" t="s">
+      <c r="S35" s="8">
+        <v>0</v>
+      </c>
+      <c r="T35" s="5">
+        <v>0</v>
+      </c>
+      <c r="U35" s="5">
+        <v>0</v>
+      </c>
+      <c r="V35" s="5">
+        <v>0</v>
+      </c>
+      <c r="W35" s="8">
+        <v>0</v>
+      </c>
+      <c r="X35" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="s">
         <v>30</v>
       </c>
-      <c r="X35" t="s">
+      <c r="AB35" t="s">
         <v>167</v>
       </c>
-      <c r="Y35" t="s">
+      <c r="AC35" t="s">
         <v>168</v>
       </c>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4"/>
-      <c r="AB35" s="4"/>
-      <c r="AC35" s="4"/>
-      <c r="AD35" s="4"/>
-      <c r="AE35" s="4"/>
+      <c r="AD35" s="3"/>
+      <c r="AE35" s="3"/>
+      <c r="AF35" s="3"/>
+      <c r="AG35" s="3"/>
+      <c r="AH35" s="3"/>
+      <c r="AI35" s="3"/>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A36" s="12" t="s">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A36" s="10" t="s">
         <v>169</v>
       </c>
       <c r="B36">
         <v>127999</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="14" t="s">
         <v>170</v>
       </c>
       <c r="D36">
@@ -4101,25 +4530,25 @@
       <c r="H36" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="7">
+      <c r="I36" s="5">
         <v>514</v>
       </c>
-      <c r="J36" s="7">
+      <c r="J36" s="5">
         <v>511</v>
       </c>
-      <c r="K36" s="8">
-        <v>0</v>
-      </c>
-      <c r="L36" s="9">
+      <c r="K36" s="6">
+        <v>0</v>
+      </c>
+      <c r="L36" s="7">
         <v>3</v>
       </c>
       <c r="M36">
         <v>0</v>
       </c>
-      <c r="N36" s="8">
-        <v>0</v>
-      </c>
-      <c r="O36" s="9">
+      <c r="N36" s="6">
+        <v>0</v>
+      </c>
+      <c r="O36" s="7">
         <v>3</v>
       </c>
       <c r="P36">
@@ -4131,44 +4560,56 @@
       <c r="R36">
         <v>0</v>
       </c>
-      <c r="S36" s="10">
-        <v>0</v>
-      </c>
-      <c r="T36" s="7">
-        <v>0</v>
-      </c>
-      <c r="U36" s="7">
-        <v>0</v>
-      </c>
-      <c r="V36" s="11">
-        <v>0</v>
-      </c>
-      <c r="W36" t="s">
+      <c r="S36" s="8">
+        <v>0</v>
+      </c>
+      <c r="T36" s="5">
+        <v>0</v>
+      </c>
+      <c r="U36" s="5">
+        <v>0</v>
+      </c>
+      <c r="V36" s="5">
+        <v>0</v>
+      </c>
+      <c r="W36" s="8">
+        <v>0</v>
+      </c>
+      <c r="X36" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="s">
         <v>30</v>
       </c>
-      <c r="X36" t="s">
+      <c r="AB36" t="s">
         <v>171</v>
       </c>
-      <c r="Y36" t="s">
+      <c r="AC36" t="s">
         <v>172</v>
       </c>
-      <c r="Z36" s="4" t="s">
+      <c r="AD36" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="AA36" s="4"/>
-      <c r="AB36" s="4"/>
-      <c r="AC36" s="4"/>
-      <c r="AD36" s="4"/>
-      <c r="AE36" s="4"/>
+      <c r="AE36" s="3"/>
+      <c r="AF36" s="3"/>
+      <c r="AG36" s="3"/>
+      <c r="AH36" s="3"/>
+      <c r="AI36" s="3"/>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A37" s="12" t="s">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A37" s="10" t="s">
         <v>174</v>
       </c>
       <c r="B37">
         <v>127999</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="14" t="s">
         <v>175</v>
       </c>
       <c r="D37">
@@ -4183,25 +4624,25 @@
       <c r="H37" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="7">
+      <c r="I37" s="5">
         <v>524</v>
       </c>
-      <c r="J37" s="7">
+      <c r="J37" s="5">
         <v>520</v>
       </c>
-      <c r="K37" s="8">
-        <v>0</v>
-      </c>
-      <c r="L37" s="9">
+      <c r="K37" s="6">
+        <v>0</v>
+      </c>
+      <c r="L37" s="7">
         <v>3</v>
       </c>
       <c r="M37">
         <v>1</v>
       </c>
-      <c r="N37" s="8">
-        <v>0</v>
-      </c>
-      <c r="O37" s="9">
+      <c r="N37" s="6">
+        <v>0</v>
+      </c>
+      <c r="O37" s="7">
         <v>2</v>
       </c>
       <c r="P37">
@@ -4213,44 +4654,56 @@
       <c r="R37">
         <v>0</v>
       </c>
-      <c r="S37" s="10">
-        <v>0</v>
-      </c>
-      <c r="T37" s="7">
-        <v>0</v>
-      </c>
-      <c r="U37" s="7">
-        <v>0</v>
-      </c>
-      <c r="V37" s="11">
-        <v>0</v>
-      </c>
-      <c r="W37" t="s">
+      <c r="S37" s="8">
+        <v>0</v>
+      </c>
+      <c r="T37" s="5">
+        <v>0</v>
+      </c>
+      <c r="U37" s="5">
+        <v>0</v>
+      </c>
+      <c r="V37" s="5">
+        <v>0</v>
+      </c>
+      <c r="W37" s="8">
+        <v>0</v>
+      </c>
+      <c r="X37" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="s">
         <v>30</v>
       </c>
-      <c r="X37" t="s">
+      <c r="AB37" t="s">
         <v>176</v>
       </c>
-      <c r="Y37" t="s">
+      <c r="AC37" t="s">
         <v>172</v>
       </c>
-      <c r="Z37" s="4" t="s">
+      <c r="AD37" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="AA37" s="4"/>
-      <c r="AB37" s="4"/>
-      <c r="AC37" s="4"/>
-      <c r="AD37" s="4"/>
-      <c r="AE37" s="4"/>
+      <c r="AE37" s="3"/>
+      <c r="AF37" s="3"/>
+      <c r="AG37" s="3"/>
+      <c r="AH37" s="3"/>
+      <c r="AI37" s="3"/>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A38" s="12" t="s">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A38" s="10" t="s">
         <v>177</v>
       </c>
       <c r="B38">
         <v>127999</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="14" t="s">
         <v>178</v>
       </c>
       <c r="D38">
@@ -4265,25 +4718,25 @@
       <c r="H38" t="s">
         <v>29</v>
       </c>
-      <c r="I38" s="7">
+      <c r="I38" s="5">
         <v>529</v>
       </c>
-      <c r="J38" s="7">
+      <c r="J38" s="5">
         <v>527</v>
       </c>
-      <c r="K38" s="8">
-        <v>1</v>
-      </c>
-      <c r="L38" s="9">
+      <c r="K38" s="6">
+        <v>1</v>
+      </c>
+      <c r="L38" s="7">
         <v>1</v>
       </c>
       <c r="M38">
         <v>0</v>
       </c>
-      <c r="N38" s="8">
-        <v>0</v>
-      </c>
-      <c r="O38" s="9">
+      <c r="N38" s="6">
+        <v>0</v>
+      </c>
+      <c r="O38" s="7">
         <v>1</v>
       </c>
       <c r="P38">
@@ -4295,44 +4748,56 @@
       <c r="R38">
         <v>0</v>
       </c>
-      <c r="S38" s="10">
-        <v>0</v>
-      </c>
-      <c r="T38" s="7">
-        <v>0</v>
-      </c>
-      <c r="U38" s="7">
-        <v>0</v>
-      </c>
-      <c r="V38" s="11">
-        <v>0</v>
-      </c>
-      <c r="W38" t="s">
+      <c r="S38" s="8">
+        <v>0</v>
+      </c>
+      <c r="T38" s="5">
+        <v>0</v>
+      </c>
+      <c r="U38" s="5">
+        <v>0</v>
+      </c>
+      <c r="V38" s="5">
+        <v>0</v>
+      </c>
+      <c r="W38" s="8">
+        <v>0</v>
+      </c>
+      <c r="X38" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="s">
         <v>30</v>
       </c>
-      <c r="X38" t="s">
+      <c r="AB38" t="s">
         <v>179</v>
       </c>
-      <c r="Y38" t="s">
+      <c r="AC38" t="s">
         <v>172</v>
       </c>
-      <c r="Z38" s="4" t="s">
+      <c r="AD38" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="AA38" s="4"/>
-      <c r="AB38" s="4"/>
-      <c r="AC38" s="4"/>
-      <c r="AD38" s="4"/>
-      <c r="AE38" s="4"/>
+      <c r="AE38" s="3"/>
+      <c r="AF38" s="3"/>
+      <c r="AG38" s="3"/>
+      <c r="AH38" s="3"/>
+      <c r="AI38" s="3"/>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A39" s="12" t="s">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A39" s="10" t="s">
         <v>181</v>
       </c>
       <c r="B39">
         <v>127999</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="14" t="s">
         <v>182</v>
       </c>
       <c r="D39">
@@ -4347,25 +4812,25 @@
       <c r="H39" t="s">
         <v>29</v>
       </c>
-      <c r="I39" s="7">
+      <c r="I39" s="5">
         <v>538</v>
       </c>
-      <c r="J39" s="7">
+      <c r="J39" s="5">
         <v>537</v>
       </c>
-      <c r="K39" s="8">
-        <v>0</v>
-      </c>
-      <c r="L39" s="9">
+      <c r="K39" s="6">
+        <v>0</v>
+      </c>
+      <c r="L39" s="7">
         <v>1</v>
       </c>
       <c r="M39">
         <v>0</v>
       </c>
-      <c r="N39" s="8">
-        <v>0</v>
-      </c>
-      <c r="O39" s="9">
+      <c r="N39" s="6">
+        <v>0</v>
+      </c>
+      <c r="O39" s="7">
         <v>1</v>
       </c>
       <c r="P39">
@@ -4377,44 +4842,56 @@
       <c r="R39">
         <v>120</v>
       </c>
-      <c r="S39" s="10">
+      <c r="S39" s="8">
         <v>0.1</v>
       </c>
-      <c r="T39" s="7">
-        <v>0</v>
-      </c>
-      <c r="U39" s="7">
-        <v>0</v>
-      </c>
-      <c r="V39" s="11">
-        <v>0</v>
-      </c>
-      <c r="W39" t="s">
+      <c r="T39" s="5">
+        <v>0</v>
+      </c>
+      <c r="U39" s="5">
+        <v>0</v>
+      </c>
+      <c r="V39" s="5">
+        <v>0</v>
+      </c>
+      <c r="W39" s="8">
+        <v>0</v>
+      </c>
+      <c r="X39" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="s">
         <v>30</v>
       </c>
-      <c r="X39" t="s">
+      <c r="AB39" t="s">
         <v>183</v>
       </c>
-      <c r="Y39" t="s">
+      <c r="AC39" t="s">
         <v>172</v>
       </c>
-      <c r="Z39" s="4" t="s">
+      <c r="AD39" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AA39" s="4"/>
-      <c r="AB39" s="4"/>
-      <c r="AC39" s="4"/>
-      <c r="AD39" s="4"/>
-      <c r="AE39" s="4"/>
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A40" s="12" t="s">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A40" s="10" t="s">
         <v>185</v>
       </c>
       <c r="B40">
         <v>127999</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="14" t="s">
         <v>186</v>
       </c>
       <c r="D40">
@@ -4429,25 +4906,25 @@
       <c r="H40" t="s">
         <v>29</v>
       </c>
-      <c r="I40" s="7">
+      <c r="I40" s="5">
         <v>662</v>
       </c>
-      <c r="J40" s="7">
+      <c r="J40" s="5">
         <v>584</v>
       </c>
-      <c r="K40" s="8">
-        <v>0</v>
-      </c>
-      <c r="L40" s="9">
+      <c r="K40" s="6">
+        <v>0</v>
+      </c>
+      <c r="L40" s="7">
         <v>78</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
-      <c r="N40" s="8">
+      <c r="N40" s="6">
         <v>3</v>
       </c>
-      <c r="O40" s="9">
+      <c r="O40" s="7">
         <v>62</v>
       </c>
       <c r="P40">
@@ -4459,44 +4936,56 @@
       <c r="R40">
         <v>0</v>
       </c>
-      <c r="S40" s="10">
-        <v>0</v>
-      </c>
-      <c r="T40" s="7">
-        <v>0</v>
-      </c>
-      <c r="U40" s="7">
-        <v>0</v>
-      </c>
-      <c r="V40" s="11">
-        <v>0</v>
-      </c>
-      <c r="W40" t="s">
+      <c r="S40" s="8">
+        <v>0</v>
+      </c>
+      <c r="T40" s="5">
+        <v>0</v>
+      </c>
+      <c r="U40" s="5">
+        <v>0</v>
+      </c>
+      <c r="V40" s="5">
+        <v>0</v>
+      </c>
+      <c r="W40" s="8">
+        <v>0</v>
+      </c>
+      <c r="X40" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="s">
         <v>30</v>
       </c>
-      <c r="X40" t="s">
+      <c r="AB40" t="s">
         <v>187</v>
       </c>
-      <c r="Y40" t="s">
+      <c r="AC40" t="s">
         <v>172</v>
       </c>
-      <c r="Z40" s="4" t="s">
+      <c r="AD40" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AA40" s="4"/>
-      <c r="AB40" s="4"/>
-      <c r="AC40" s="4"/>
-      <c r="AD40" s="4"/>
-      <c r="AE40" s="4"/>
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A41" s="12" t="s">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A41" s="10" t="s">
         <v>188</v>
       </c>
       <c r="B41">
         <v>127999</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="14" t="s">
         <v>189</v>
       </c>
       <c r="D41">
@@ -4511,25 +5000,25 @@
       <c r="H41" t="s">
         <v>29</v>
       </c>
-      <c r="I41" s="7">
+      <c r="I41" s="5">
         <v>878</v>
       </c>
-      <c r="J41" s="7">
+      <c r="J41" s="5">
         <v>777</v>
       </c>
-      <c r="K41" s="8">
-        <v>0</v>
-      </c>
-      <c r="L41" s="9">
+      <c r="K41" s="6">
+        <v>0</v>
+      </c>
+      <c r="L41" s="7">
         <v>101</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
-      <c r="N41" s="8">
+      <c r="N41" s="6">
         <v>2</v>
       </c>
-      <c r="O41" s="9">
+      <c r="O41" s="7">
         <v>104</v>
       </c>
       <c r="P41">
@@ -4541,44 +5030,56 @@
       <c r="R41">
         <v>0</v>
       </c>
-      <c r="S41" s="10">
-        <v>0</v>
-      </c>
-      <c r="T41" s="7">
-        <v>0</v>
-      </c>
-      <c r="U41" s="7">
-        <v>0</v>
-      </c>
-      <c r="V41" s="11">
-        <v>0</v>
-      </c>
-      <c r="W41" t="s">
+      <c r="S41" s="8">
+        <v>0</v>
+      </c>
+      <c r="T41" s="5">
+        <v>0</v>
+      </c>
+      <c r="U41" s="5">
+        <v>0</v>
+      </c>
+      <c r="V41" s="5">
+        <v>0</v>
+      </c>
+      <c r="W41" s="8">
+        <v>0</v>
+      </c>
+      <c r="X41" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="s">
         <v>30</v>
       </c>
-      <c r="X41" t="s">
+      <c r="AB41" t="s">
         <v>190</v>
       </c>
-      <c r="Y41" t="s">
+      <c r="AC41" t="s">
         <v>172</v>
       </c>
-      <c r="Z41" s="4" t="s">
+      <c r="AD41" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="AA41" s="4"/>
-      <c r="AB41" s="4"/>
-      <c r="AC41" s="4"/>
-      <c r="AD41" s="4"/>
-      <c r="AE41" s="4"/>
+      <c r="AE41" s="3"/>
+      <c r="AF41" s="3"/>
+      <c r="AG41" s="3"/>
+      <c r="AH41" s="3"/>
+      <c r="AI41" s="3"/>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A42" s="12" t="s">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A42" s="10" t="s">
         <v>192</v>
       </c>
       <c r="B42">
         <v>127999</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="14" t="s">
         <v>193</v>
       </c>
       <c r="D42">
@@ -4593,25 +5094,25 @@
       <c r="H42" t="s">
         <v>29</v>
       </c>
-      <c r="I42" s="7">
+      <c r="I42" s="5">
         <v>726</v>
       </c>
-      <c r="J42" s="7">
+      <c r="J42" s="5">
         <v>666</v>
       </c>
-      <c r="K42" s="8">
-        <v>0</v>
-      </c>
-      <c r="L42" s="9">
+      <c r="K42" s="6">
+        <v>0</v>
+      </c>
+      <c r="L42" s="7">
         <v>60</v>
       </c>
       <c r="M42">
         <v>0</v>
       </c>
-      <c r="N42" s="8">
-        <v>1</v>
-      </c>
-      <c r="O42" s="9">
+      <c r="N42" s="6">
+        <v>1</v>
+      </c>
+      <c r="O42" s="7">
         <v>55</v>
       </c>
       <c r="P42">
@@ -4623,44 +5124,56 @@
       <c r="R42">
         <v>0</v>
       </c>
-      <c r="S42" s="10">
-        <v>0</v>
-      </c>
-      <c r="T42" s="7">
-        <v>0</v>
-      </c>
-      <c r="U42" s="7">
-        <v>0</v>
-      </c>
-      <c r="V42" s="11">
-        <v>0</v>
-      </c>
-      <c r="W42" t="s">
+      <c r="S42" s="8">
+        <v>0</v>
+      </c>
+      <c r="T42" s="5">
+        <v>0</v>
+      </c>
+      <c r="U42" s="5">
+        <v>0</v>
+      </c>
+      <c r="V42" s="5">
+        <v>0</v>
+      </c>
+      <c r="W42" s="8">
+        <v>0</v>
+      </c>
+      <c r="X42" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="s">
         <v>30</v>
       </c>
-      <c r="X42" t="s">
+      <c r="AB42" t="s">
         <v>194</v>
       </c>
-      <c r="Y42" t="s">
+      <c r="AC42" t="s">
         <v>172</v>
       </c>
-      <c r="Z42" s="4" t="s">
+      <c r="AD42" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AA42" s="4"/>
-      <c r="AB42" s="4"/>
-      <c r="AC42" s="4"/>
-      <c r="AD42" s="4"/>
-      <c r="AE42" s="4"/>
+      <c r="AE42" s="3"/>
+      <c r="AF42" s="3"/>
+      <c r="AG42" s="3"/>
+      <c r="AH42" s="3"/>
+      <c r="AI42" s="3"/>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A43" s="12" t="s">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A43" s="10" t="s">
         <v>195</v>
       </c>
       <c r="B43">
         <v>127999</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="14" t="s">
         <v>196</v>
       </c>
       <c r="D43">
@@ -4675,25 +5188,25 @@
       <c r="H43" t="s">
         <v>29</v>
       </c>
-      <c r="I43" s="7">
+      <c r="I43" s="5">
         <v>1048</v>
       </c>
-      <c r="J43" s="7">
+      <c r="J43" s="5">
         <v>989</v>
       </c>
-      <c r="K43" s="8">
-        <v>0</v>
-      </c>
-      <c r="L43" s="9">
+      <c r="K43" s="6">
+        <v>0</v>
+      </c>
+      <c r="L43" s="7">
         <v>59</v>
       </c>
       <c r="M43">
         <v>0</v>
       </c>
-      <c r="N43" s="8">
+      <c r="N43" s="6">
         <v>2</v>
       </c>
-      <c r="O43" s="9">
+      <c r="O43" s="7">
         <v>61</v>
       </c>
       <c r="P43">
@@ -4705,44 +5218,56 @@
       <c r="R43">
         <v>0</v>
       </c>
-      <c r="S43" s="10">
-        <v>0</v>
-      </c>
-      <c r="T43" s="7">
-        <v>0</v>
-      </c>
-      <c r="U43" s="7">
-        <v>0</v>
-      </c>
-      <c r="V43" s="11">
-        <v>0</v>
-      </c>
-      <c r="W43" t="s">
+      <c r="S43" s="8">
+        <v>0</v>
+      </c>
+      <c r="T43" s="5">
+        <v>0</v>
+      </c>
+      <c r="U43" s="5">
+        <v>0</v>
+      </c>
+      <c r="V43" s="5">
+        <v>0</v>
+      </c>
+      <c r="W43" s="8">
+        <v>0</v>
+      </c>
+      <c r="X43" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="s">
         <v>30</v>
       </c>
-      <c r="X43" t="s">
+      <c r="AB43" t="s">
         <v>197</v>
       </c>
-      <c r="Y43" t="s">
+      <c r="AC43" t="s">
         <v>172</v>
       </c>
-      <c r="Z43" s="4" t="s">
+      <c r="AD43" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AA43" s="4"/>
-      <c r="AB43" s="4"/>
-      <c r="AC43" s="4"/>
-      <c r="AD43" s="4"/>
-      <c r="AE43" s="4"/>
+      <c r="AE43" s="3"/>
+      <c r="AF43" s="3"/>
+      <c r="AG43" s="3"/>
+      <c r="AH43" s="3"/>
+      <c r="AI43" s="3"/>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A44" s="12" t="s">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A44" s="10" t="s">
         <v>198</v>
       </c>
       <c r="B44">
         <v>127999</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="14" t="s">
         <v>199</v>
       </c>
       <c r="D44">
@@ -4757,25 +5282,25 @@
       <c r="H44" t="s">
         <v>29</v>
       </c>
-      <c r="I44" s="7">
+      <c r="I44" s="5">
         <v>811</v>
       </c>
-      <c r="J44" s="7">
+      <c r="J44" s="5">
         <v>755</v>
       </c>
-      <c r="K44" s="8">
-        <v>1</v>
-      </c>
-      <c r="L44" s="9">
+      <c r="K44" s="6">
+        <v>1</v>
+      </c>
+      <c r="L44" s="7">
         <v>55</v>
       </c>
       <c r="M44">
         <v>0</v>
       </c>
-      <c r="N44" s="8">
-        <v>0</v>
-      </c>
-      <c r="O44" s="9">
+      <c r="N44" s="6">
+        <v>0</v>
+      </c>
+      <c r="O44" s="7">
         <v>57</v>
       </c>
       <c r="P44">
@@ -4787,44 +5312,56 @@
       <c r="R44">
         <v>73</v>
       </c>
-      <c r="S44" s="10">
+      <c r="S44" s="8">
         <v>0.1</v>
       </c>
-      <c r="T44" s="7">
-        <v>0</v>
-      </c>
-      <c r="U44" s="7">
-        <v>0</v>
-      </c>
-      <c r="V44" s="11">
-        <v>0</v>
-      </c>
-      <c r="W44" t="s">
+      <c r="T44" s="5">
+        <v>0</v>
+      </c>
+      <c r="U44" s="5">
+        <v>0</v>
+      </c>
+      <c r="V44" s="5">
+        <v>0</v>
+      </c>
+      <c r="W44" s="8">
+        <v>0</v>
+      </c>
+      <c r="X44" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="s">
         <v>30</v>
       </c>
-      <c r="X44" t="s">
+      <c r="AB44" t="s">
         <v>200</v>
       </c>
-      <c r="Y44" t="s">
+      <c r="AC44" t="s">
         <v>172</v>
       </c>
-      <c r="Z44" s="4" t="s">
+      <c r="AD44" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AA44" s="4"/>
-      <c r="AB44" s="4"/>
-      <c r="AC44" s="4"/>
-      <c r="AD44" s="4"/>
-      <c r="AE44" s="4"/>
+      <c r="AE44" s="3"/>
+      <c r="AF44" s="3"/>
+      <c r="AG44" s="3"/>
+      <c r="AH44" s="3"/>
+      <c r="AI44" s="3"/>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A45" s="12" t="s">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A45" s="10" t="s">
         <v>201</v>
       </c>
       <c r="B45">
         <v>127999</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="14" t="s">
         <v>202</v>
       </c>
       <c r="D45">
@@ -4839,25 +5376,25 @@
       <c r="H45" t="s">
         <v>29</v>
       </c>
-      <c r="I45" s="7">
+      <c r="I45" s="5">
         <v>756</v>
       </c>
-      <c r="J45" s="7">
+      <c r="J45" s="5">
         <v>703</v>
       </c>
-      <c r="K45" s="8">
-        <v>1</v>
-      </c>
-      <c r="L45" s="9">
+      <c r="K45" s="6">
+        <v>1</v>
+      </c>
+      <c r="L45" s="7">
         <v>52</v>
       </c>
       <c r="M45">
         <v>0</v>
       </c>
-      <c r="N45" s="8">
-        <v>1</v>
-      </c>
-      <c r="O45" s="9">
+      <c r="N45" s="6">
+        <v>1</v>
+      </c>
+      <c r="O45" s="7">
         <v>53</v>
       </c>
       <c r="P45">
@@ -4869,44 +5406,56 @@
       <c r="R45">
         <v>0</v>
       </c>
-      <c r="S45" s="10">
-        <v>0</v>
-      </c>
-      <c r="T45" s="7">
-        <v>0</v>
-      </c>
-      <c r="U45" s="7">
-        <v>0</v>
-      </c>
-      <c r="V45" s="11">
-        <v>0</v>
-      </c>
-      <c r="W45" t="s">
+      <c r="S45" s="8">
+        <v>0</v>
+      </c>
+      <c r="T45" s="5">
+        <v>0</v>
+      </c>
+      <c r="U45" s="5">
+        <v>0</v>
+      </c>
+      <c r="V45" s="5">
+        <v>0</v>
+      </c>
+      <c r="W45" s="8">
+        <v>0</v>
+      </c>
+      <c r="X45" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="s">
         <v>30</v>
       </c>
-      <c r="X45" t="s">
+      <c r="AB45" t="s">
         <v>203</v>
       </c>
-      <c r="Y45" t="s">
+      <c r="AC45" t="s">
         <v>172</v>
       </c>
-      <c r="Z45" s="4" t="s">
+      <c r="AD45" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AA45" s="4"/>
-      <c r="AB45" s="4"/>
-      <c r="AC45" s="4"/>
-      <c r="AD45" s="4"/>
-      <c r="AE45" s="4"/>
+      <c r="AE45" s="3"/>
+      <c r="AF45" s="3"/>
+      <c r="AG45" s="3"/>
+      <c r="AH45" s="3"/>
+      <c r="AI45" s="3"/>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A46" s="12" t="s">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A46" s="10" t="s">
         <v>204</v>
       </c>
       <c r="B46">
         <v>127999</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="14" t="s">
         <v>205</v>
       </c>
       <c r="D46">
@@ -4921,25 +5470,25 @@
       <c r="H46" t="s">
         <v>29</v>
       </c>
-      <c r="I46" s="7">
+      <c r="I46" s="5">
         <v>843</v>
       </c>
-      <c r="J46" s="7">
+      <c r="J46" s="5">
         <v>738</v>
       </c>
-      <c r="K46" s="8">
-        <v>0</v>
-      </c>
-      <c r="L46" s="9">
+      <c r="K46" s="6">
+        <v>0</v>
+      </c>
+      <c r="L46" s="7">
         <v>105</v>
       </c>
       <c r="M46">
         <v>0</v>
       </c>
-      <c r="N46" s="8">
-        <v>1</v>
-      </c>
-      <c r="O46" s="9">
+      <c r="N46" s="6">
+        <v>1</v>
+      </c>
+      <c r="O46" s="7">
         <v>105</v>
       </c>
       <c r="P46">
@@ -4951,44 +5500,56 @@
       <c r="R46">
         <v>542</v>
       </c>
-      <c r="S46" s="10">
+      <c r="S46" s="8">
         <v>0.4</v>
       </c>
-      <c r="T46" s="7">
-        <v>0</v>
-      </c>
-      <c r="U46" s="7">
-        <v>0</v>
-      </c>
-      <c r="V46" s="11">
-        <v>0</v>
-      </c>
-      <c r="W46" t="s">
+      <c r="T46" s="5">
+        <v>0</v>
+      </c>
+      <c r="U46" s="5">
+        <v>0</v>
+      </c>
+      <c r="V46" s="5">
+        <v>0</v>
+      </c>
+      <c r="W46" s="8">
+        <v>0</v>
+      </c>
+      <c r="X46" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="s">
         <v>30</v>
       </c>
-      <c r="X46" t="s">
+      <c r="AB46" t="s">
         <v>206</v>
       </c>
-      <c r="Y46" t="s">
+      <c r="AC46" t="s">
         <v>172</v>
       </c>
-      <c r="Z46" s="4" t="s">
+      <c r="AD46" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AA46" s="4"/>
-      <c r="AB46" s="4"/>
-      <c r="AC46" s="4"/>
-      <c r="AD46" s="4"/>
-      <c r="AE46" s="4"/>
+      <c r="AE46" s="3"/>
+      <c r="AF46" s="3"/>
+      <c r="AG46" s="3"/>
+      <c r="AH46" s="3"/>
+      <c r="AI46" s="3"/>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A47" s="12" t="s">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A47" s="10" t="s">
         <v>207</v>
       </c>
       <c r="B47">
         <v>127999</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="14" t="s">
         <v>208</v>
       </c>
       <c r="D47">
@@ -5003,25 +5564,25 @@
       <c r="H47" t="s">
         <v>29</v>
       </c>
-      <c r="I47" s="7">
+      <c r="I47" s="5">
         <v>821</v>
       </c>
-      <c r="J47" s="7">
+      <c r="J47" s="5">
         <v>772</v>
       </c>
-      <c r="K47" s="8">
-        <v>0</v>
-      </c>
-      <c r="L47" s="9">
+      <c r="K47" s="6">
+        <v>0</v>
+      </c>
+      <c r="L47" s="7">
         <v>49</v>
       </c>
       <c r="M47">
         <v>0</v>
       </c>
-      <c r="N47" s="8">
-        <v>0</v>
-      </c>
-      <c r="O47" s="9">
+      <c r="N47" s="6">
+        <v>0</v>
+      </c>
+      <c r="O47" s="7">
         <v>47</v>
       </c>
       <c r="P47">
@@ -5033,44 +5594,56 @@
       <c r="R47">
         <v>0</v>
       </c>
-      <c r="S47" s="10">
-        <v>0</v>
-      </c>
-      <c r="T47" s="7">
-        <v>0</v>
-      </c>
-      <c r="U47" s="7">
-        <v>0</v>
-      </c>
-      <c r="V47" s="11">
-        <v>0</v>
-      </c>
-      <c r="W47" t="s">
+      <c r="S47" s="8">
+        <v>0</v>
+      </c>
+      <c r="T47" s="5">
+        <v>0</v>
+      </c>
+      <c r="U47" s="5">
+        <v>0</v>
+      </c>
+      <c r="V47" s="5">
+        <v>0</v>
+      </c>
+      <c r="W47" s="8">
+        <v>0</v>
+      </c>
+      <c r="X47" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="s">
         <v>30</v>
       </c>
-      <c r="X47" t="s">
+      <c r="AB47" t="s">
         <v>209</v>
       </c>
-      <c r="Y47" t="s">
+      <c r="AC47" t="s">
         <v>172</v>
       </c>
-      <c r="Z47" s="4" t="s">
+      <c r="AD47" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="AA47" s="4"/>
-      <c r="AB47" s="4"/>
-      <c r="AC47" s="4"/>
-      <c r="AD47" s="4"/>
-      <c r="AE47" s="4"/>
+      <c r="AE47" s="3"/>
+      <c r="AF47" s="3"/>
+      <c r="AG47" s="3"/>
+      <c r="AH47" s="3"/>
+      <c r="AI47" s="3"/>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A48" s="12" t="s">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A48" s="10" t="s">
         <v>211</v>
       </c>
       <c r="B48">
         <v>127999</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="14" t="s">
         <v>212</v>
       </c>
       <c r="D48">
@@ -5085,25 +5658,25 @@
       <c r="H48" t="s">
         <v>29</v>
       </c>
-      <c r="I48" s="7">
+      <c r="I48" s="5">
         <v>967</v>
       </c>
-      <c r="J48" s="7">
+      <c r="J48" s="5">
         <v>919</v>
       </c>
-      <c r="K48" s="8">
-        <v>1</v>
-      </c>
-      <c r="L48" s="9">
+      <c r="K48" s="6">
+        <v>1</v>
+      </c>
+      <c r="L48" s="7">
         <v>47</v>
       </c>
       <c r="M48">
         <v>0</v>
       </c>
-      <c r="N48" s="8">
-        <v>0</v>
-      </c>
-      <c r="O48" s="9">
+      <c r="N48" s="6">
+        <v>0</v>
+      </c>
+      <c r="O48" s="7">
         <v>57</v>
       </c>
       <c r="P48">
@@ -5115,44 +5688,56 @@
       <c r="R48">
         <v>393</v>
       </c>
-      <c r="S48" s="10">
+      <c r="S48" s="8">
         <v>0.3</v>
       </c>
-      <c r="T48" s="7">
-        <v>0</v>
-      </c>
-      <c r="U48" s="7">
-        <v>0</v>
-      </c>
-      <c r="V48" s="11">
-        <v>0</v>
-      </c>
-      <c r="W48" t="s">
+      <c r="T48" s="5">
+        <v>0</v>
+      </c>
+      <c r="U48" s="5">
+        <v>0</v>
+      </c>
+      <c r="V48" s="5">
+        <v>0</v>
+      </c>
+      <c r="W48" s="8">
+        <v>0</v>
+      </c>
+      <c r="X48" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="s">
         <v>30</v>
       </c>
-      <c r="X48" t="s">
+      <c r="AB48" t="s">
         <v>213</v>
       </c>
-      <c r="Y48" t="s">
+      <c r="AC48" t="s">
         <v>172</v>
       </c>
-      <c r="Z48" s="4" t="s">
+      <c r="AD48" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="AA48" s="4"/>
-      <c r="AB48" s="4"/>
-      <c r="AC48" s="4"/>
-      <c r="AD48" s="4"/>
-      <c r="AE48" s="4"/>
+      <c r="AE48" s="3"/>
+      <c r="AF48" s="3"/>
+      <c r="AG48" s="3"/>
+      <c r="AH48" s="3"/>
+      <c r="AI48" s="3"/>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A49" s="12" t="s">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A49" s="10" t="s">
         <v>214</v>
       </c>
       <c r="B49">
         <v>127999</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="14" t="s">
         <v>215</v>
       </c>
       <c r="D49">
@@ -5167,25 +5752,25 @@
       <c r="H49" t="s">
         <v>29</v>
       </c>
-      <c r="I49" s="7">
+      <c r="I49" s="5">
         <v>695</v>
       </c>
-      <c r="J49" s="7">
+      <c r="J49" s="5">
         <v>665</v>
       </c>
-      <c r="K49" s="8">
-        <v>0</v>
-      </c>
-      <c r="L49" s="9">
+      <c r="K49" s="6">
+        <v>0</v>
+      </c>
+      <c r="L49" s="7">
         <v>30</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
-      <c r="N49" s="8">
-        <v>1</v>
-      </c>
-      <c r="O49" s="9">
+      <c r="N49" s="6">
+        <v>1</v>
+      </c>
+      <c r="O49" s="7">
         <v>29</v>
       </c>
       <c r="P49">
@@ -5197,44 +5782,56 @@
       <c r="R49">
         <v>950</v>
       </c>
-      <c r="S49" s="10">
+      <c r="S49" s="8">
         <v>0.7</v>
       </c>
-      <c r="T49" s="7">
-        <v>0</v>
-      </c>
-      <c r="U49" s="7">
-        <v>0</v>
-      </c>
-      <c r="V49" s="11">
-        <v>0</v>
-      </c>
-      <c r="W49" t="s">
+      <c r="T49" s="5">
+        <v>0</v>
+      </c>
+      <c r="U49" s="5">
+        <v>0</v>
+      </c>
+      <c r="V49" s="5">
+        <v>0</v>
+      </c>
+      <c r="W49" s="8">
+        <v>0</v>
+      </c>
+      <c r="X49" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="s">
         <v>30</v>
       </c>
-      <c r="X49" t="s">
+      <c r="AB49" t="s">
         <v>216</v>
       </c>
-      <c r="Y49" t="s">
+      <c r="AC49" t="s">
         <v>172</v>
       </c>
-      <c r="Z49" s="4" t="s">
+      <c r="AD49" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="AA49" s="4"/>
-      <c r="AB49" s="4"/>
-      <c r="AC49" s="4"/>
-      <c r="AD49" s="4"/>
-      <c r="AE49" s="4"/>
+      <c r="AE49" s="3"/>
+      <c r="AF49" s="3"/>
+      <c r="AG49" s="3"/>
+      <c r="AH49" s="3"/>
+      <c r="AI49" s="3"/>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A50" s="12" t="s">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A50" s="10" t="s">
         <v>218</v>
       </c>
       <c r="B50">
         <v>127999</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="14" t="s">
         <v>219</v>
       </c>
       <c r="D50">
@@ -5249,25 +5846,25 @@
       <c r="H50" t="s">
         <v>29</v>
       </c>
-      <c r="I50" s="7">
+      <c r="I50" s="5">
         <v>777</v>
       </c>
-      <c r="J50" s="7">
+      <c r="J50" s="5">
         <v>760</v>
       </c>
-      <c r="K50" s="8">
-        <v>0</v>
-      </c>
-      <c r="L50" s="9">
+      <c r="K50" s="6">
+        <v>0</v>
+      </c>
+      <c r="L50" s="7">
         <v>17</v>
       </c>
       <c r="M50">
         <v>0</v>
       </c>
-      <c r="N50" s="8">
-        <v>1</v>
-      </c>
-      <c r="O50" s="9">
+      <c r="N50" s="6">
+        <v>1</v>
+      </c>
+      <c r="O50" s="7">
         <v>21</v>
       </c>
       <c r="P50">
@@ -5279,44 +5876,56 @@
       <c r="R50">
         <v>0</v>
       </c>
-      <c r="S50" s="10">
-        <v>0</v>
-      </c>
-      <c r="T50" s="7">
-        <v>0</v>
-      </c>
-      <c r="U50" s="7">
-        <v>0</v>
-      </c>
-      <c r="V50" s="11">
-        <v>0</v>
-      </c>
-      <c r="W50" t="s">
+      <c r="S50" s="8">
+        <v>0</v>
+      </c>
+      <c r="T50" s="5">
+        <v>0</v>
+      </c>
+      <c r="U50" s="5">
+        <v>0</v>
+      </c>
+      <c r="V50" s="5">
+        <v>0</v>
+      </c>
+      <c r="W50" s="8">
+        <v>0</v>
+      </c>
+      <c r="X50" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="s">
         <v>30</v>
       </c>
-      <c r="X50" t="s">
+      <c r="AB50" t="s">
         <v>220</v>
       </c>
-      <c r="Y50" t="s">
+      <c r="AC50" t="s">
         <v>172</v>
       </c>
-      <c r="Z50" s="4" t="s">
+      <c r="AD50" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AA50" s="4"/>
-      <c r="AB50" s="4"/>
-      <c r="AC50" s="4"/>
-      <c r="AD50" s="4"/>
-      <c r="AE50" s="4"/>
+      <c r="AE50" s="3"/>
+      <c r="AF50" s="3"/>
+      <c r="AG50" s="3"/>
+      <c r="AH50" s="3"/>
+      <c r="AI50" s="3"/>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A51" s="12" t="s">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A51" s="10" t="s">
         <v>221</v>
       </c>
       <c r="B51">
         <v>63999</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="14" t="s">
         <v>222</v>
       </c>
       <c r="D51">
@@ -5331,25 +5940,25 @@
       <c r="H51" t="s">
         <v>29</v>
       </c>
-      <c r="I51" s="7">
+      <c r="I51" s="5">
         <v>417</v>
       </c>
-      <c r="J51" s="7">
+      <c r="J51" s="5">
         <v>404</v>
       </c>
-      <c r="K51" s="8">
-        <v>0</v>
-      </c>
-      <c r="L51" s="9">
+      <c r="K51" s="6">
+        <v>0</v>
+      </c>
+      <c r="L51" s="7">
         <v>13</v>
       </c>
       <c r="M51">
         <v>0</v>
       </c>
-      <c r="N51" s="8">
-        <v>0</v>
-      </c>
-      <c r="O51" s="9">
+      <c r="N51" s="6">
+        <v>0</v>
+      </c>
+      <c r="O51" s="7">
         <v>13</v>
       </c>
       <c r="P51">
@@ -5361,44 +5970,56 @@
       <c r="R51">
         <v>0</v>
       </c>
-      <c r="S51" s="10">
-        <v>0</v>
-      </c>
-      <c r="T51" s="7">
-        <v>0</v>
-      </c>
-      <c r="U51" s="7">
-        <v>0</v>
-      </c>
-      <c r="V51" s="11">
-        <v>0</v>
-      </c>
-      <c r="W51" t="s">
+      <c r="S51" s="8">
+        <v>0</v>
+      </c>
+      <c r="T51" s="5">
+        <v>0</v>
+      </c>
+      <c r="U51" s="5">
+        <v>0</v>
+      </c>
+      <c r="V51" s="5">
+        <v>0</v>
+      </c>
+      <c r="W51" s="8">
+        <v>0</v>
+      </c>
+      <c r="X51" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="s">
         <v>30</v>
       </c>
-      <c r="X51" t="s">
+      <c r="AB51" t="s">
         <v>223</v>
       </c>
-      <c r="Y51" t="s">
+      <c r="AC51" t="s">
         <v>172</v>
       </c>
-      <c r="Z51" s="4" t="s">
+      <c r="AD51" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="4"/>
-      <c r="AC51" s="4"/>
-      <c r="AD51" s="4"/>
-      <c r="AE51" s="4"/>
+      <c r="AE51" s="3"/>
+      <c r="AF51" s="3"/>
+      <c r="AG51" s="3"/>
+      <c r="AH51" s="3"/>
+      <c r="AI51" s="3"/>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A52" s="12" t="s">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A52" s="10" t="s">
         <v>224</v>
       </c>
       <c r="B52">
         <v>127999</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="14" t="s">
         <v>225</v>
       </c>
       <c r="D52">
@@ -5413,25 +6034,25 @@
       <c r="H52" t="s">
         <v>226</v>
       </c>
-      <c r="I52" s="7">
+      <c r="I52" s="5">
         <v>961</v>
       </c>
-      <c r="J52" s="7">
+      <c r="J52" s="5">
         <v>952</v>
       </c>
-      <c r="K52" s="8">
+      <c r="K52" s="6">
         <v>9</v>
       </c>
-      <c r="L52" s="9">
+      <c r="L52" s="7">
         <v>0</v>
       </c>
       <c r="M52">
         <v>0</v>
       </c>
-      <c r="N52" s="8">
+      <c r="N52" s="6">
         <v>6</v>
       </c>
-      <c r="O52" s="9">
+      <c r="O52" s="7">
         <v>4</v>
       </c>
       <c r="P52">
@@ -5443,44 +6064,56 @@
       <c r="R52">
         <v>235</v>
       </c>
-      <c r="S52" s="10">
+      <c r="S52" s="8">
         <v>0.2</v>
       </c>
-      <c r="T52" s="7">
-        <v>0</v>
-      </c>
-      <c r="U52" s="7">
-        <v>0</v>
-      </c>
-      <c r="V52" s="11">
-        <v>0</v>
-      </c>
-      <c r="W52" t="s">
+      <c r="T52" s="5">
+        <v>0</v>
+      </c>
+      <c r="U52" s="5">
+        <v>0</v>
+      </c>
+      <c r="V52" s="5">
+        <v>0</v>
+      </c>
+      <c r="W52" s="8">
+        <v>0</v>
+      </c>
+      <c r="X52" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="s">
         <v>30</v>
       </c>
-      <c r="X52" t="s">
+      <c r="AB52" t="s">
         <v>227</v>
       </c>
-      <c r="Y52" t="s">
+      <c r="AC52" t="s">
         <v>228</v>
       </c>
-      <c r="Z52" s="4" t="s">
+      <c r="AD52" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AA52" s="4"/>
-      <c r="AB52" s="4"/>
-      <c r="AC52" s="4"/>
-      <c r="AD52" s="4"/>
-      <c r="AE52" s="4"/>
+      <c r="AE52" s="3"/>
+      <c r="AF52" s="3"/>
+      <c r="AG52" s="3"/>
+      <c r="AH52" s="3"/>
+      <c r="AI52" s="3"/>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A53" s="12" t="s">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A53" s="10" t="s">
         <v>229</v>
       </c>
       <c r="B53">
         <v>127999</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="14" t="s">
         <v>230</v>
       </c>
       <c r="D53">
@@ -5495,25 +6128,25 @@
       <c r="H53" t="s">
         <v>226</v>
       </c>
-      <c r="I53" s="7">
+      <c r="I53" s="5">
         <v>917</v>
       </c>
-      <c r="J53" s="7">
+      <c r="J53" s="5">
         <v>912</v>
       </c>
-      <c r="K53" s="8">
+      <c r="K53" s="6">
         <v>5</v>
       </c>
-      <c r="L53" s="9">
+      <c r="L53" s="7">
         <v>0</v>
       </c>
       <c r="M53">
         <v>0</v>
       </c>
-      <c r="N53" s="8">
-        <v>0</v>
-      </c>
-      <c r="O53" s="9">
+      <c r="N53" s="6">
+        <v>0</v>
+      </c>
+      <c r="O53" s="7">
         <v>4</v>
       </c>
       <c r="P53">
@@ -5525,44 +6158,56 @@
       <c r="R53">
         <v>0</v>
       </c>
-      <c r="S53" s="10">
-        <v>0</v>
-      </c>
-      <c r="T53" s="7">
-        <v>0</v>
-      </c>
-      <c r="U53" s="7">
-        <v>0</v>
-      </c>
-      <c r="V53" s="11">
-        <v>0</v>
-      </c>
-      <c r="W53" t="s">
+      <c r="S53" s="8">
+        <v>0</v>
+      </c>
+      <c r="T53" s="5">
+        <v>0</v>
+      </c>
+      <c r="U53" s="5">
+        <v>0</v>
+      </c>
+      <c r="V53" s="5">
+        <v>0</v>
+      </c>
+      <c r="W53" s="8">
+        <v>0</v>
+      </c>
+      <c r="X53" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="s">
         <v>30</v>
       </c>
-      <c r="X53" t="s">
+      <c r="AB53" t="s">
         <v>231</v>
       </c>
-      <c r="Y53" t="s">
+      <c r="AC53" t="s">
         <v>228</v>
       </c>
-      <c r="Z53" s="4" t="s">
+      <c r="AD53" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AA53" s="4"/>
-      <c r="AB53" s="4"/>
-      <c r="AC53" s="4"/>
-      <c r="AD53" s="4"/>
-      <c r="AE53" s="4"/>
+      <c r="AE53" s="3"/>
+      <c r="AF53" s="3"/>
+      <c r="AG53" s="3"/>
+      <c r="AH53" s="3"/>
+      <c r="AI53" s="3"/>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A54" s="12" t="s">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A54" s="10" t="s">
         <v>232</v>
       </c>
       <c r="B54">
         <v>127999</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="14" t="s">
         <v>233</v>
       </c>
       <c r="D54">
@@ -5580,25 +6225,25 @@
       <c r="H54" t="s">
         <v>29</v>
       </c>
-      <c r="I54" s="7">
+      <c r="I54" s="5">
         <v>502</v>
       </c>
-      <c r="J54" s="7">
+      <c r="J54" s="5">
         <v>501</v>
       </c>
-      <c r="K54" s="8">
-        <v>1</v>
-      </c>
-      <c r="L54" s="9">
+      <c r="K54" s="6">
+        <v>1</v>
+      </c>
+      <c r="L54" s="7">
         <v>0</v>
       </c>
       <c r="M54">
         <v>0</v>
       </c>
-      <c r="N54" s="8">
+      <c r="N54" s="6">
         <v>58</v>
       </c>
-      <c r="O54" s="9">
+      <c r="O54" s="7">
         <v>0</v>
       </c>
       <c r="P54">
@@ -5610,44 +6255,56 @@
       <c r="R54">
         <v>0</v>
       </c>
-      <c r="S54" s="10">
-        <v>0</v>
-      </c>
-      <c r="T54" s="7">
-        <v>0</v>
-      </c>
-      <c r="U54" s="7">
-        <v>0</v>
-      </c>
-      <c r="V54" s="11">
-        <v>0</v>
-      </c>
-      <c r="W54" t="s">
+      <c r="S54" s="8">
+        <v>0</v>
+      </c>
+      <c r="T54" s="5">
+        <v>0</v>
+      </c>
+      <c r="U54" s="5">
+        <v>0</v>
+      </c>
+      <c r="V54" s="5">
+        <v>0</v>
+      </c>
+      <c r="W54" s="8">
+        <v>0</v>
+      </c>
+      <c r="X54" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="s">
         <v>30</v>
       </c>
-      <c r="X54" t="s">
+      <c r="AB54" t="s">
         <v>235</v>
       </c>
-      <c r="Y54" t="s">
+      <c r="AC54" t="s">
         <v>228</v>
       </c>
-      <c r="Z54" s="4" t="s">
+      <c r="AD54" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="AA54" s="4"/>
-      <c r="AB54" s="4"/>
-      <c r="AC54" s="4"/>
-      <c r="AD54" s="4"/>
-      <c r="AE54" s="4"/>
+      <c r="AE54" s="3"/>
+      <c r="AF54" s="3"/>
+      <c r="AG54" s="3"/>
+      <c r="AH54" s="3"/>
+      <c r="AI54" s="3"/>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A55" s="12" t="s">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A55" s="10" t="s">
         <v>237</v>
       </c>
       <c r="B55">
         <v>127999</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="14" t="s">
         <v>238</v>
       </c>
       <c r="D55">
@@ -5665,25 +6322,25 @@
       <c r="H55" t="s">
         <v>29</v>
       </c>
-      <c r="I55" s="7">
+      <c r="I55" s="5">
         <v>530</v>
       </c>
-      <c r="J55" s="7">
+      <c r="J55" s="5">
         <v>530</v>
       </c>
-      <c r="K55" s="8">
-        <v>0</v>
-      </c>
-      <c r="L55" s="9">
+      <c r="K55" s="6">
+        <v>0</v>
+      </c>
+      <c r="L55" s="7">
         <v>0</v>
       </c>
       <c r="M55">
         <v>0</v>
       </c>
-      <c r="N55" s="8">
+      <c r="N55" s="6">
         <v>35</v>
       </c>
-      <c r="O55" s="9">
+      <c r="O55" s="7">
         <v>0</v>
       </c>
       <c r="P55">
@@ -5695,35 +6352,47 @@
       <c r="R55">
         <v>0</v>
       </c>
-      <c r="S55" s="10">
-        <v>0</v>
-      </c>
-      <c r="T55" s="7">
-        <v>0</v>
-      </c>
-      <c r="U55" s="7">
-        <v>0</v>
-      </c>
-      <c r="V55" s="11">
-        <v>0</v>
-      </c>
-      <c r="W55" t="s">
+      <c r="S55" s="8">
+        <v>0</v>
+      </c>
+      <c r="T55" s="5">
+        <v>0</v>
+      </c>
+      <c r="U55" s="5">
+        <v>0</v>
+      </c>
+      <c r="V55" s="5">
+        <v>0</v>
+      </c>
+      <c r="W55" s="8">
+        <v>0</v>
+      </c>
+      <c r="X55" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="s">
         <v>30</v>
       </c>
-      <c r="X55" t="s">
+      <c r="AB55" t="s">
         <v>239</v>
       </c>
-      <c r="Y55" t="s">
+      <c r="AC55" t="s">
         <v>228</v>
       </c>
-      <c r="Z55" s="4" t="s">
+      <c r="AD55" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="AA55" s="4"/>
-      <c r="AB55" s="4"/>
-      <c r="AC55" s="4"/>
-      <c r="AD55" s="4"/>
-      <c r="AE55" s="4"/>
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
